--- a/research/traditional_assets/database/data/romania/romania_restaurant_dining.xlsx
+++ b/research/traditional_assets/database/data/romania/romania_restaurant_dining.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1071509003594644</v>
+        <v>0.1070172589188892</v>
       </c>
       <c r="C2">
-        <v>430.6968179822194</v>
+        <v>427.2245207646758</v>
       </c>
       <c r="D2">
-        <v>407.3968179822194</v>
+        <v>408.1525207646758</v>
       </c>
       <c r="E2">
-        <v>-97.59999999999999</v>
+        <v>-93.372</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>4.228</v>
       </c>
       <c r="G2">
         <v>23.3</v>
@@ -1451,28 +1451,28 @@
         <v>21.8</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.2126684</v>
       </c>
       <c r="N2">
-        <v>21.8</v>
+        <v>21.5873316</v>
       </c>
       <c r="O2">
-        <v>3.488</v>
+        <v>3.453973056000001</v>
       </c>
       <c r="P2">
-        <v>18.312</v>
+        <v>18.133358544</v>
       </c>
       <c r="Q2">
-        <v>40.612</v>
+        <v>40.433358544</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1071509003594644</v>
+        <v>0.1076714534534235</v>
       </c>
       <c r="T2">
-        <v>0.8445182362326225</v>
+        <v>0.8516838455097477</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>102.5070015103325</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1070172589188892</v>
+        <v>0.1068836174783141</v>
       </c>
       <c r="C3">
-        <v>427.2245207646758</v>
+        <v>423.7550323467054</v>
       </c>
       <c r="D3">
-        <v>408.1525207646758</v>
+        <v>408.9110323467054</v>
       </c>
       <c r="E3">
-        <v>-93.372</v>
+        <v>-89.14399999999999</v>
       </c>
       <c r="F3">
-        <v>4.228</v>
+        <v>8.456</v>
       </c>
       <c r="G3">
         <v>23.3</v>
@@ -1533,28 +1533,28 @@
         <v>21.8</v>
       </c>
       <c r="M3">
-        <v>0.2126684</v>
+        <v>0.4253368</v>
       </c>
       <c r="N3">
-        <v>21.5873316</v>
+        <v>21.3746632</v>
       </c>
       <c r="O3">
-        <v>3.453973056000001</v>
+        <v>3.419946112</v>
       </c>
       <c r="P3">
-        <v>18.133358544</v>
+        <v>17.954717088</v>
       </c>
       <c r="Q3">
-        <v>40.433358544</v>
+        <v>40.254717088</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1076714534534235</v>
+        <v>0.1082026300799124</v>
       </c>
       <c r="T3">
-        <v>0.8516838455097477</v>
+        <v>0.858995691710896</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>102.5070015103325</v>
+        <v>51.25350075516626</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1068836174783141</v>
+        <v>0.106749976037739</v>
       </c>
       <c r="C4">
-        <v>423.7550323467054</v>
+        <v>420.288368417103</v>
       </c>
       <c r="D4">
-        <v>408.9110323467054</v>
+        <v>409.672368417103</v>
       </c>
       <c r="E4">
-        <v>-89.14399999999999</v>
+        <v>-84.916</v>
       </c>
       <c r="F4">
-        <v>8.456</v>
+        <v>12.684</v>
       </c>
       <c r="G4">
         <v>23.3</v>
@@ -1615,28 +1615,28 @@
         <v>21.8</v>
       </c>
       <c r="M4">
-        <v>0.4253368</v>
+        <v>0.6380051999999998</v>
       </c>
       <c r="N4">
-        <v>21.3746632</v>
+        <v>21.1619948</v>
       </c>
       <c r="O4">
-        <v>3.419946112</v>
+        <v>3.385919168</v>
       </c>
       <c r="P4">
-        <v>17.954717088</v>
+        <v>17.776075632</v>
       </c>
       <c r="Q4">
-        <v>40.254717088</v>
+        <v>40.076075632</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1082026300799124</v>
+        <v>0.1087447588017928</v>
       </c>
       <c r="T4">
-        <v>0.858995691710896</v>
+        <v>0.8664582976275318</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>51.25350075516626</v>
+        <v>34.16900050344419</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.106749976037739</v>
+        <v>0.1066163345971638</v>
       </c>
       <c r="C5">
-        <v>420.288368417103</v>
+        <v>416.8245447817231</v>
       </c>
       <c r="D5">
-        <v>409.672368417103</v>
+        <v>410.4365447817231</v>
       </c>
       <c r="E5">
-        <v>-84.916</v>
+        <v>-80.68799999999999</v>
       </c>
       <c r="F5">
-        <v>12.684</v>
+        <v>16.912</v>
       </c>
       <c r="G5">
         <v>23.3</v>
@@ -1697,28 +1697,28 @@
         <v>21.8</v>
       </c>
       <c r="M5">
-        <v>0.6380051999999998</v>
+        <v>0.8506735999999999</v>
       </c>
       <c r="N5">
-        <v>21.1619948</v>
+        <v>20.9493264</v>
       </c>
       <c r="O5">
-        <v>3.385919168</v>
+        <v>3.351892224</v>
       </c>
       <c r="P5">
-        <v>17.776075632</v>
+        <v>17.597434176</v>
       </c>
       <c r="Q5">
-        <v>40.076075632</v>
+        <v>39.897434176</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1087447588017928</v>
+        <v>0.1092981818720457</v>
       </c>
       <c r="T5">
-        <v>0.8664582976275318</v>
+        <v>0.8740763745007641</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>34.16900050344419</v>
+        <v>25.62675037758313</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1066163345971638</v>
+        <v>0.1064826931565887</v>
       </c>
       <c r="C6">
-        <v>416.8245447817231</v>
+        <v>413.3635773645729</v>
       </c>
       <c r="D6">
-        <v>410.4365447817231</v>
+        <v>411.2035773645729</v>
       </c>
       <c r="E6">
-        <v>-80.68799999999999</v>
+        <v>-76.45999999999999</v>
       </c>
       <c r="F6">
-        <v>16.912</v>
+        <v>21.14</v>
       </c>
       <c r="G6">
         <v>23.3</v>
@@ -1779,28 +1779,28 @@
         <v>21.8</v>
       </c>
       <c r="M6">
-        <v>0.8506735999999999</v>
+        <v>1.063342</v>
       </c>
       <c r="N6">
-        <v>20.9493264</v>
+        <v>20.736658</v>
       </c>
       <c r="O6">
-        <v>3.351892224</v>
+        <v>3.31786528</v>
       </c>
       <c r="P6">
-        <v>17.597434176</v>
+        <v>17.41879272</v>
       </c>
       <c r="Q6">
-        <v>39.897434176</v>
+        <v>39.71879272</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1092981818720457</v>
+        <v>0.1098632559543039</v>
       </c>
       <c r="T6">
-        <v>0.8740763745007641</v>
+        <v>0.8818548319397489</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>25.62675037758313</v>
+        <v>20.5014003020665</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1064826931565887</v>
+        <v>0.1063490517160136</v>
       </c>
       <c r="C7">
-        <v>413.3635773645729</v>
+        <v>409.9054822089195</v>
       </c>
       <c r="D7">
-        <v>411.2035773645729</v>
+        <v>411.9734822089195</v>
       </c>
       <c r="E7">
-        <v>-76.45999999999999</v>
+        <v>-72.232</v>
       </c>
       <c r="F7">
-        <v>21.14</v>
+        <v>25.368</v>
       </c>
       <c r="G7">
         <v>23.3</v>
@@ -1861,28 +1861,28 @@
         <v>21.8</v>
       </c>
       <c r="M7">
-        <v>1.063342</v>
+        <v>1.2760104</v>
       </c>
       <c r="N7">
-        <v>20.736658</v>
+        <v>20.5239896</v>
       </c>
       <c r="O7">
-        <v>3.31786528</v>
+        <v>3.283838336</v>
       </c>
       <c r="P7">
-        <v>17.41879272</v>
+        <v>17.240151264</v>
       </c>
       <c r="Q7">
-        <v>39.71879272</v>
+        <v>39.540151264</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1098632559543039</v>
+        <v>0.1104403528893761</v>
       </c>
       <c r="T7">
-        <v>0.8818548319397489</v>
+        <v>0.8897987884731802</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>20.5014003020665</v>
+        <v>17.08450025172209</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1063490517160136</v>
+        <v>0.1062154102754384</v>
       </c>
       <c r="C8">
-        <v>409.9054822089195</v>
+        <v>406.4502754784078</v>
       </c>
       <c r="D8">
-        <v>411.9734822089195</v>
+        <v>412.7462754784078</v>
       </c>
       <c r="E8">
-        <v>-72.232</v>
+        <v>-68.004</v>
       </c>
       <c r="F8">
-        <v>25.36799999999999</v>
+        <v>29.59599999999999</v>
       </c>
       <c r="G8">
         <v>23.3</v>
@@ -1943,28 +1943,28 @@
         <v>21.8</v>
       </c>
       <c r="M8">
-        <v>1.2760104</v>
+        <v>1.4886788</v>
       </c>
       <c r="N8">
-        <v>20.5239896</v>
+        <v>20.3113212</v>
       </c>
       <c r="O8">
-        <v>3.283838336</v>
+        <v>3.249811392</v>
       </c>
       <c r="P8">
-        <v>17.240151264</v>
+        <v>17.061509808</v>
       </c>
       <c r="Q8">
-        <v>39.540151264</v>
+        <v>39.361509808</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1104403528893761</v>
+        <v>0.1110298605112241</v>
       </c>
       <c r="T8">
-        <v>0.8897987884731802</v>
+        <v>0.8979135827815238</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>17.08450025172209</v>
+        <v>14.64385735861894</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1062154102754384</v>
+        <v>0.1061825688348633</v>
       </c>
       <c r="C9">
-        <v>406.4502754784079</v>
+        <v>402.41262795263</v>
       </c>
       <c r="D9">
-        <v>412.7462754784079</v>
+        <v>412.93662795263</v>
       </c>
       <c r="E9">
-        <v>-68.00399999999999</v>
+        <v>-63.776</v>
       </c>
       <c r="F9">
-        <v>29.596</v>
+        <v>33.824</v>
       </c>
       <c r="G9">
         <v>23.3</v>
@@ -2025,45 +2025,45 @@
         <v>21.8</v>
       </c>
       <c r="M9">
-        <v>1.4886788</v>
+        <v>1.7520832</v>
       </c>
       <c r="N9">
-        <v>20.3113212</v>
+        <v>20.0479168</v>
       </c>
       <c r="O9">
-        <v>3.249811392</v>
+        <v>3.207666688</v>
       </c>
       <c r="P9">
-        <v>17.061509808</v>
+        <v>16.840250112</v>
       </c>
       <c r="Q9">
-        <v>39.361509808</v>
+        <v>39.140250112</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1110298605112241</v>
+        <v>0.1116321835161557</v>
       </c>
       <c r="T9">
-        <v>0.8979135827815238</v>
+        <v>0.9062047856617879</v>
       </c>
       <c r="U9">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V9">
         <v>0.16</v>
       </c>
       <c r="W9">
-        <v>0.042252</v>
+        <v>0.043512</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y9">
-        <v>14.64385735861893</v>
+        <v>12.44233150571845</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1061825688348633</v>
+        <v>0.1060615273942881</v>
       </c>
       <c r="C10">
-        <v>402.41262795263</v>
+        <v>398.8877156178967</v>
       </c>
       <c r="D10">
-        <v>412.93662795263</v>
+        <v>413.6397156178967</v>
       </c>
       <c r="E10">
-        <v>-63.776</v>
+        <v>-59.548</v>
       </c>
       <c r="F10">
-        <v>33.824</v>
+        <v>38.05199999999999</v>
       </c>
       <c r="G10">
         <v>23.3</v>
@@ -2107,28 +2107,28 @@
         <v>21.8</v>
       </c>
       <c r="M10">
-        <v>1.7520832</v>
+        <v>1.9710936</v>
       </c>
       <c r="N10">
-        <v>20.0479168</v>
+        <v>19.8289064</v>
       </c>
       <c r="O10">
-        <v>3.207666688</v>
+        <v>3.172625024</v>
       </c>
       <c r="P10">
-        <v>16.840250112</v>
+        <v>16.656281376</v>
       </c>
       <c r="Q10">
-        <v>39.140250112</v>
+        <v>38.95628137600001</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1116321835161557</v>
+        <v>0.1122477443893276</v>
       </c>
       <c r="T10">
-        <v>0.9062047856617879</v>
+        <v>0.9146782127811788</v>
       </c>
       <c r="U10">
         <v>0.0518</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>12.44233150571845</v>
+        <v>11.05985022730529</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1060615273942881</v>
+        <v>0.105940485953713</v>
       </c>
       <c r="C11">
-        <v>398.8877156178967</v>
+        <v>395.3652015948813</v>
       </c>
       <c r="D11">
-        <v>413.6397156178967</v>
+        <v>414.3452015948812</v>
       </c>
       <c r="E11">
-        <v>-59.548</v>
+        <v>-55.32</v>
       </c>
       <c r="F11">
-        <v>38.05199999999999</v>
+        <v>42.27999999999999</v>
       </c>
       <c r="G11">
         <v>23.3</v>
@@ -2189,28 +2189,28 @@
         <v>21.8</v>
       </c>
       <c r="M11">
-        <v>1.9710936</v>
+        <v>2.190104</v>
       </c>
       <c r="N11">
-        <v>19.8289064</v>
+        <v>19.609896</v>
       </c>
       <c r="O11">
-        <v>3.172625024</v>
+        <v>3.13758336</v>
       </c>
       <c r="P11">
-        <v>16.656281376</v>
+        <v>16.47231264</v>
       </c>
       <c r="Q11">
-        <v>38.95628137600001</v>
+        <v>38.77231264</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1122477443893276</v>
+        <v>0.1128769843930144</v>
       </c>
       <c r="T11">
-        <v>0.9146782127811788</v>
+        <v>0.9233399382810005</v>
       </c>
       <c r="U11">
         <v>0.0518</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>11.05985022730529</v>
+        <v>9.953865204574761</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.105940485953713</v>
+        <v>0.1059765245131378</v>
       </c>
       <c r="C12">
-        <v>395.3652015948812</v>
+        <v>390.9269006010409</v>
       </c>
       <c r="D12">
-        <v>414.3452015948812</v>
+        <v>414.1349006010408</v>
       </c>
       <c r="E12">
-        <v>-55.31999999999999</v>
+        <v>-51.092</v>
       </c>
       <c r="F12">
-        <v>42.28</v>
+        <v>46.508</v>
       </c>
       <c r="G12">
         <v>23.3</v>
@@ -2271,45 +2271,45 @@
         <v>21.8</v>
       </c>
       <c r="M12">
-        <v>2.190104</v>
+        <v>2.488178</v>
       </c>
       <c r="N12">
-        <v>19.609896</v>
+        <v>19.311822</v>
       </c>
       <c r="O12">
-        <v>3.13758336</v>
+        <v>3.08989152</v>
       </c>
       <c r="P12">
-        <v>16.47231264</v>
+        <v>16.22193048</v>
       </c>
       <c r="Q12">
-        <v>38.77231264</v>
+        <v>38.52193047999999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1128769843930144</v>
+        <v>0.1135203646215032</v>
       </c>
       <c r="T12">
-        <v>0.9233399382810005</v>
+        <v>0.9321963092976723</v>
       </c>
       <c r="U12">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V12">
         <v>0.16</v>
       </c>
       <c r="W12">
-        <v>0.043512</v>
+        <v>0.04494</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y12">
-        <v>9.953865204574761</v>
+        <v>8.761431055173706</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1059765245131378</v>
+        <v>0.1058697630725627</v>
       </c>
       <c r="C13">
-        <v>390.9269006010409</v>
+        <v>387.3225224646018</v>
       </c>
       <c r="D13">
-        <v>414.1349006010408</v>
+        <v>414.7585224646018</v>
       </c>
       <c r="E13">
-        <v>-51.092</v>
+        <v>-46.864</v>
       </c>
       <c r="F13">
-        <v>46.508</v>
+        <v>50.73599999999999</v>
       </c>
       <c r="G13">
         <v>23.3</v>
@@ -2353,28 +2353,28 @@
         <v>21.8</v>
       </c>
       <c r="M13">
-        <v>2.488178</v>
+        <v>2.714375999999999</v>
       </c>
       <c r="N13">
-        <v>19.311822</v>
+        <v>19.085624</v>
       </c>
       <c r="O13">
-        <v>3.08989152</v>
+        <v>3.053699840000001</v>
       </c>
       <c r="P13">
-        <v>16.22193048</v>
+        <v>16.03192416</v>
       </c>
       <c r="Q13">
-        <v>38.52193047999999</v>
+        <v>38.33192416</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1135203646215032</v>
+        <v>0.1141783671279121</v>
       </c>
       <c r="T13">
-        <v>0.9321963092976723</v>
+        <v>0.9412539614738137</v>
       </c>
       <c r="U13">
         <v>0.0535</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>8.761431055173706</v>
+        <v>8.031311800575899</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1058697630725627</v>
+        <v>0.1058503616319875</v>
       </c>
       <c r="C14">
-        <v>387.3225224646018</v>
+        <v>383.2080531433726</v>
       </c>
       <c r="D14">
-        <v>414.7585224646018</v>
+        <v>414.8720531433726</v>
       </c>
       <c r="E14">
-        <v>-46.864</v>
+        <v>-42.636</v>
       </c>
       <c r="F14">
-        <v>50.73599999999999</v>
+        <v>54.964</v>
       </c>
       <c r="G14">
         <v>23.3</v>
@@ -2435,45 +2435,45 @@
         <v>21.8</v>
       </c>
       <c r="M14">
-        <v>2.714375999999999</v>
+        <v>2.9845452</v>
       </c>
       <c r="N14">
-        <v>19.085624</v>
+        <v>18.8154548</v>
       </c>
       <c r="O14">
-        <v>3.053699840000001</v>
+        <v>3.010472768</v>
       </c>
       <c r="P14">
-        <v>16.03192416</v>
+        <v>15.804982032</v>
       </c>
       <c r="Q14">
-        <v>38.33192416</v>
+        <v>38.104982032</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1141783671279121</v>
+        <v>0.1148514961287213</v>
       </c>
       <c r="T14">
-        <v>0.9412539614738137</v>
+        <v>0.9505198355390621</v>
       </c>
       <c r="U14">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V14">
         <v>0.16</v>
       </c>
       <c r="W14">
-        <v>0.04494</v>
+        <v>0.045612</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y14">
-        <v>8.031311800575899</v>
+        <v>7.304295475236898</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1058503616319875</v>
+        <v>0.1057503201914124</v>
       </c>
       <c r="C15">
-        <v>383.2080531433726</v>
+        <v>379.5664497803605</v>
       </c>
       <c r="D15">
-        <v>414.8720531433726</v>
+        <v>415.4584497803605</v>
       </c>
       <c r="E15">
-        <v>-42.636</v>
+        <v>-38.40799999999999</v>
       </c>
       <c r="F15">
-        <v>54.964</v>
+        <v>59.192</v>
       </c>
       <c r="G15">
         <v>23.3</v>
@@ -2517,28 +2517,28 @@
         <v>21.8</v>
       </c>
       <c r="M15">
-        <v>2.9845452</v>
+        <v>3.2141256</v>
       </c>
       <c r="N15">
-        <v>18.8154548</v>
+        <v>18.5858744</v>
       </c>
       <c r="O15">
-        <v>3.010472768</v>
+        <v>2.973739904</v>
       </c>
       <c r="P15">
-        <v>15.804982032</v>
+        <v>15.612134496</v>
       </c>
       <c r="Q15">
-        <v>38.104982032</v>
+        <v>37.912134496</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1148514961287213</v>
+        <v>0.11554027929234</v>
       </c>
       <c r="T15">
-        <v>0.9505198355390621</v>
+        <v>0.9600011950476881</v>
       </c>
       <c r="U15">
         <v>0.0543</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>7.304295475236898</v>
+        <v>6.782560084148548</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1057503201914124</v>
+        <v>0.1056502787508372</v>
       </c>
       <c r="C16">
-        <v>379.5664497803605</v>
+        <v>375.9265064362773</v>
       </c>
       <c r="D16">
-        <v>415.4584497803605</v>
+        <v>416.0465064362773</v>
       </c>
       <c r="E16">
-        <v>-38.40799999999999</v>
+        <v>-34.17999999999999</v>
       </c>
       <c r="F16">
-        <v>59.192</v>
+        <v>63.42</v>
       </c>
       <c r="G16">
         <v>23.3</v>
@@ -2599,28 +2599,28 @@
         <v>21.8</v>
       </c>
       <c r="M16">
-        <v>3.2141256</v>
+        <v>3.443706</v>
       </c>
       <c r="N16">
-        <v>18.5858744</v>
+        <v>18.356294</v>
       </c>
       <c r="O16">
-        <v>2.973739904</v>
+        <v>2.937007040000001</v>
       </c>
       <c r="P16">
-        <v>15.612134496</v>
+        <v>15.41928696</v>
       </c>
       <c r="Q16">
-        <v>37.912134496</v>
+        <v>37.71928696000001</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.11554027929234</v>
+        <v>0.1162452691186321</v>
       </c>
       <c r="T16">
-        <v>0.9600011950476881</v>
+        <v>0.9697056453682817</v>
       </c>
       <c r="U16">
         <v>0.0543</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>6.782560084148548</v>
+        <v>6.330389411871978</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1056502787508372</v>
+        <v>0.1056846373102621</v>
       </c>
       <c r="C17">
-        <v>375.9265064362774</v>
+        <v>371.4963547383325</v>
       </c>
       <c r="D17">
-        <v>416.0465064362773</v>
+        <v>415.8443547383324</v>
       </c>
       <c r="E17">
-        <v>-34.18000000000001</v>
+        <v>-29.952</v>
       </c>
       <c r="F17">
-        <v>63.41999999999999</v>
+        <v>67.648</v>
       </c>
       <c r="G17">
         <v>23.3</v>
@@ -2681,45 +2681,45 @@
         <v>21.8</v>
       </c>
       <c r="M17">
-        <v>3.443705999999999</v>
+        <v>3.7409344</v>
       </c>
       <c r="N17">
-        <v>18.356294</v>
+        <v>18.0590656</v>
       </c>
       <c r="O17">
-        <v>2.937007040000001</v>
+        <v>2.889450496</v>
       </c>
       <c r="P17">
-        <v>15.41928696</v>
+        <v>15.169615104</v>
       </c>
       <c r="Q17">
-        <v>37.71928696000001</v>
+        <v>37.469615104</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1162452691186321</v>
+        <v>0.1169670444169787</v>
       </c>
       <c r="T17">
-        <v>0.9697056453682817</v>
+        <v>0.979641154029842</v>
       </c>
       <c r="U17">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V17">
         <v>0.16</v>
       </c>
       <c r="W17">
-        <v>0.045612</v>
+        <v>0.046452</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y17">
-        <v>6.330389411871979</v>
+        <v>5.827421084956742</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1056846373102621</v>
+        <v>0.105592995869687</v>
       </c>
       <c r="C18">
-        <v>371.4963547383325</v>
+        <v>367.8079728022886</v>
       </c>
       <c r="D18">
-        <v>415.8443547383324</v>
+        <v>416.3839728022886</v>
       </c>
       <c r="E18">
-        <v>-29.952</v>
+        <v>-25.724</v>
       </c>
       <c r="F18">
-        <v>67.648</v>
+        <v>71.87599999999999</v>
       </c>
       <c r="G18">
         <v>23.3</v>
@@ -2763,28 +2763,28 @@
         <v>21.8</v>
       </c>
       <c r="M18">
-        <v>3.7409344</v>
+        <v>3.9747428</v>
       </c>
       <c r="N18">
-        <v>18.0590656</v>
+        <v>17.8252572</v>
       </c>
       <c r="O18">
-        <v>2.889450496</v>
+        <v>2.852041152</v>
       </c>
       <c r="P18">
-        <v>15.169615104</v>
+        <v>14.973216048</v>
       </c>
       <c r="Q18">
-        <v>37.469615104</v>
+        <v>37.273216048</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1169670444169787</v>
+        <v>0.1177062118911891</v>
       </c>
       <c r="T18">
-        <v>0.979641154029842</v>
+        <v>0.9898160725386689</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>5.827421084956742</v>
+        <v>5.484631609371053</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.105592995869687</v>
+        <v>0.1055013544291118</v>
       </c>
       <c r="C19">
-        <v>367.8079728022886</v>
+        <v>364.1209931505399</v>
       </c>
       <c r="D19">
-        <v>416.3839728022886</v>
+        <v>416.9249931505399</v>
       </c>
       <c r="E19">
-        <v>-25.724</v>
+        <v>-21.496</v>
       </c>
       <c r="F19">
-        <v>71.87599999999999</v>
+        <v>76.104</v>
       </c>
       <c r="G19">
         <v>23.3</v>
@@ -2845,28 +2845,28 @@
         <v>21.8</v>
       </c>
       <c r="M19">
-        <v>3.9747428</v>
+        <v>4.2085512</v>
       </c>
       <c r="N19">
-        <v>17.8252572</v>
+        <v>17.5914488</v>
       </c>
       <c r="O19">
-        <v>2.852041152</v>
+        <v>2.814631808000001</v>
       </c>
       <c r="P19">
-        <v>14.973216048</v>
+        <v>14.776816992</v>
       </c>
       <c r="Q19">
-        <v>37.273216048</v>
+        <v>37.076816992</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1177062118911891</v>
+        <v>0.1184634078403803</v>
       </c>
       <c r="T19">
-        <v>0.9898160725386689</v>
+        <v>1.000239159791613</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>5.484631609371053</v>
+        <v>5.179929853294882</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1055013544291118</v>
+        <v>0.1054097129885367</v>
       </c>
       <c r="C20">
-        <v>364.1209931505398</v>
+        <v>360.4354212562894</v>
       </c>
       <c r="D20">
-        <v>416.9249931505398</v>
+        <v>417.4674212562894</v>
       </c>
       <c r="E20">
-        <v>-21.49600000000001</v>
+        <v>-17.268</v>
       </c>
       <c r="F20">
-        <v>76.10399999999998</v>
+        <v>80.33199999999999</v>
       </c>
       <c r="G20">
         <v>23.3</v>
@@ -2927,28 +2927,28 @@
         <v>21.8</v>
       </c>
       <c r="M20">
-        <v>4.2085512</v>
+        <v>4.4423596</v>
       </c>
       <c r="N20">
-        <v>17.5914488</v>
+        <v>17.3576404</v>
       </c>
       <c r="O20">
-        <v>2.814631808000001</v>
+        <v>2.777222464</v>
       </c>
       <c r="P20">
-        <v>14.776816992</v>
+        <v>14.580417936</v>
       </c>
       <c r="Q20">
-        <v>37.076816992</v>
+        <v>36.880417936</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1184634078403803</v>
+        <v>0.1192392999858478</v>
       </c>
       <c r="T20">
-        <v>1.000239159791613</v>
+        <v>1.010919607223643</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.179929853294883</v>
+        <v>4.907301966279363</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1054097129885367</v>
+        <v>0.1053180715479616</v>
       </c>
       <c r="C21">
-        <v>360.4354212562894</v>
+        <v>356.7512626212607</v>
       </c>
       <c r="D21">
-        <v>417.4674212562894</v>
+        <v>418.0112626212606</v>
       </c>
       <c r="E21">
-        <v>-17.268</v>
+        <v>-13.03999999999999</v>
       </c>
       <c r="F21">
-        <v>80.33199999999999</v>
+        <v>84.56</v>
       </c>
       <c r="G21">
         <v>23.3</v>
@@ -3009,28 +3009,28 @@
         <v>21.8</v>
       </c>
       <c r="M21">
-        <v>4.4423596</v>
+        <v>4.676168000000001</v>
       </c>
       <c r="N21">
-        <v>17.3576404</v>
+        <v>17.123832</v>
       </c>
       <c r="O21">
-        <v>2.777222464</v>
+        <v>2.73981312</v>
       </c>
       <c r="P21">
-        <v>14.580417936</v>
+        <v>14.38401888</v>
       </c>
       <c r="Q21">
-        <v>36.880417936</v>
+        <v>36.68401888</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1192392999858478</v>
+        <v>0.1200345894349519</v>
       </c>
       <c r="T21">
-        <v>1.010919607223643</v>
+        <v>1.021867065841473</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>4.907301966279363</v>
+        <v>4.661936867965394</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1053180715479616</v>
+        <v>0.1056674301073864</v>
       </c>
       <c r="C22">
-        <v>356.7512626212607</v>
+        <v>350.4575703141207</v>
       </c>
       <c r="D22">
-        <v>418.0112626212606</v>
+        <v>415.9455703141207</v>
       </c>
       <c r="E22">
-        <v>-13.03999999999999</v>
+        <v>-8.811999999999998</v>
       </c>
       <c r="F22">
-        <v>84.56</v>
+        <v>88.788</v>
       </c>
       <c r="G22">
         <v>23.3</v>
@@ -3091,45 +3091,45 @@
         <v>21.8</v>
       </c>
       <c r="M22">
-        <v>4.676168000000001</v>
+        <v>5.1319464</v>
       </c>
       <c r="N22">
-        <v>17.123832</v>
+        <v>16.6680536</v>
       </c>
       <c r="O22">
-        <v>2.73981312</v>
+        <v>2.666888576</v>
       </c>
       <c r="P22">
-        <v>14.38401888</v>
+        <v>14.001165024</v>
       </c>
       <c r="Q22">
-        <v>36.68401888</v>
+        <v>36.301165024</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1200345894349519</v>
+        <v>0.12085001279416</v>
       </c>
       <c r="T22">
-        <v>1.021867065841473</v>
+        <v>1.033091675310388</v>
       </c>
       <c r="U22">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V22">
         <v>0.16</v>
       </c>
       <c r="W22">
-        <v>0.046452</v>
+        <v>0.048552</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y22">
-        <v>4.661936867965394</v>
+        <v>4.247900952356011</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1056674301073864</v>
+        <v>0.1055967886668113</v>
       </c>
       <c r="C23">
-        <v>350.4575703141207</v>
+        <v>346.6456116563644</v>
       </c>
       <c r="D23">
-        <v>415.9455703141207</v>
+        <v>416.3616116563643</v>
       </c>
       <c r="E23">
-        <v>-8.812000000000012</v>
+        <v>-4.584000000000003</v>
       </c>
       <c r="F23">
-        <v>88.78799999999998</v>
+        <v>93.01599999999999</v>
       </c>
       <c r="G23">
         <v>23.3</v>
@@ -3173,28 +3173,28 @@
         <v>21.8</v>
       </c>
       <c r="M23">
-        <v>5.131946399999999</v>
+        <v>5.3763248</v>
       </c>
       <c r="N23">
-        <v>16.6680536</v>
+        <v>16.4236752</v>
       </c>
       <c r="O23">
-        <v>2.666888576</v>
+        <v>2.627788032</v>
       </c>
       <c r="P23">
-        <v>14.001165024</v>
+        <v>13.795887168</v>
       </c>
       <c r="Q23">
-        <v>36.301165024</v>
+        <v>36.095887168</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.12085001279416</v>
+        <v>0.1216863444446298</v>
       </c>
       <c r="T23">
-        <v>1.033091675310388</v>
+        <v>1.044604095278505</v>
       </c>
       <c r="U23">
         <v>0.0578</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>4.247900952356011</v>
+        <v>4.054814545430737</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1055967886668113</v>
+        <v>0.1062023472262361</v>
       </c>
       <c r="C24">
-        <v>346.6456116563644</v>
+        <v>338.8779692741714</v>
       </c>
       <c r="D24">
-        <v>416.3616116563643</v>
+        <v>412.8219692741714</v>
       </c>
       <c r="E24">
-        <v>-4.584000000000003</v>
+        <v>-0.3559999999999945</v>
       </c>
       <c r="F24">
-        <v>93.01599999999999</v>
+        <v>97.244</v>
       </c>
       <c r="G24">
         <v>23.3</v>
@@ -3255,45 +3255,45 @@
         <v>21.8</v>
       </c>
       <c r="M24">
-        <v>5.3763248</v>
+        <v>5.9610572</v>
       </c>
       <c r="N24">
-        <v>16.4236752</v>
+        <v>15.8389428</v>
       </c>
       <c r="O24">
-        <v>2.627788032</v>
+        <v>2.534230848</v>
       </c>
       <c r="P24">
-        <v>13.795887168</v>
+        <v>13.304711952</v>
       </c>
       <c r="Q24">
-        <v>36.095887168</v>
+        <v>35.604711952</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1216863444446298</v>
+        <v>0.1225443989951119</v>
       </c>
       <c r="T24">
-        <v>1.044604095278505</v>
+        <v>1.056415539141899</v>
       </c>
       <c r="U24">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V24">
         <v>0.16</v>
       </c>
       <c r="W24">
-        <v>0.048552</v>
+        <v>0.051492</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>4.054814545430737</v>
+        <v>3.657069420504806</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1062023472262361</v>
+        <v>0.106161105785661</v>
       </c>
       <c r="C25">
-        <v>338.8779692741714</v>
+        <v>334.8891249590738</v>
       </c>
       <c r="D25">
-        <v>412.8219692741714</v>
+        <v>413.0611249590738</v>
       </c>
       <c r="E25">
-        <v>-0.3559999999999945</v>
+        <v>3.872</v>
       </c>
       <c r="F25">
-        <v>97.244</v>
+        <v>101.472</v>
       </c>
       <c r="G25">
         <v>23.3</v>
@@ -3337,28 +3337,28 @@
         <v>21.8</v>
       </c>
       <c r="M25">
-        <v>5.9610572</v>
+        <v>6.220233599999999</v>
       </c>
       <c r="N25">
-        <v>15.8389428</v>
+        <v>15.5797664</v>
       </c>
       <c r="O25">
-        <v>2.534230848</v>
+        <v>2.492762624</v>
       </c>
       <c r="P25">
-        <v>13.304711952</v>
+        <v>13.087003776</v>
       </c>
       <c r="Q25">
-        <v>35.604711952</v>
+        <v>35.387003776</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1225443989951119</v>
+        <v>0.1234250339285013</v>
       </c>
       <c r="T25">
-        <v>1.056415539141899</v>
+        <v>1.068537810475381</v>
       </c>
       <c r="U25">
         <v>0.0613</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>3.657069420504806</v>
+        <v>3.504691527983772</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.106161105785661</v>
+        <v>0.1067078643450858</v>
       </c>
       <c r="C26">
-        <v>334.8891249590739</v>
+        <v>327.5128604379481</v>
       </c>
       <c r="D26">
-        <v>413.0611249590738</v>
+        <v>409.912860437948</v>
       </c>
       <c r="E26">
-        <v>3.871999999999986</v>
+        <v>8.099999999999994</v>
       </c>
       <c r="F26">
-        <v>101.472</v>
+        <v>105.7</v>
       </c>
       <c r="G26">
         <v>23.3</v>
@@ -3419,45 +3419,45 @@
         <v>21.8</v>
       </c>
       <c r="M26">
-        <v>6.220233599999998</v>
+        <v>6.77537</v>
       </c>
       <c r="N26">
-        <v>15.5797664</v>
+        <v>15.02463</v>
       </c>
       <c r="O26">
-        <v>2.492762624</v>
+        <v>2.4039408</v>
       </c>
       <c r="P26">
-        <v>13.087003776</v>
+        <v>12.6206892</v>
       </c>
       <c r="Q26">
-        <v>35.387003776</v>
+        <v>34.9206892</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1234250339285013</v>
+        <v>0.1243291524601144</v>
       </c>
       <c r="T26">
-        <v>1.068537810475381</v>
+        <v>1.080983342377757</v>
       </c>
       <c r="U26">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V26">
         <v>0.16</v>
       </c>
       <c r="W26">
-        <v>0.051492</v>
+        <v>0.053844</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y26">
-        <v>3.504691527983773</v>
+        <v>3.21753645926348</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1067078643450858</v>
+        <v>0.1066901429045107</v>
       </c>
       <c r="C27">
-        <v>327.5128604379481</v>
+        <v>323.3861487112062</v>
       </c>
       <c r="D27">
-        <v>409.912860437948</v>
+        <v>410.0141487112062</v>
       </c>
       <c r="E27">
-        <v>8.099999999999994</v>
+        <v>12.328</v>
       </c>
       <c r="F27">
-        <v>105.7</v>
+        <v>109.928</v>
       </c>
       <c r="G27">
         <v>23.3</v>
@@ -3501,28 +3501,28 @@
         <v>21.8</v>
       </c>
       <c r="M27">
-        <v>6.77537</v>
+        <v>7.0463848</v>
       </c>
       <c r="N27">
-        <v>15.02463</v>
+        <v>14.7536152</v>
       </c>
       <c r="O27">
-        <v>2.4039408</v>
+        <v>2.360578432</v>
       </c>
       <c r="P27">
-        <v>12.6206892</v>
+        <v>12.393036768</v>
       </c>
       <c r="Q27">
-        <v>34.9206892</v>
+        <v>34.693036768</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1243291524601144</v>
+        <v>0.1252577066277172</v>
       </c>
       <c r="T27">
-        <v>1.080983342377757</v>
+        <v>1.093765240007224</v>
       </c>
       <c r="U27">
         <v>0.0641</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>3.21753645926348</v>
+        <v>3.093785056984115</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1066901429045107</v>
+        <v>0.1084414614639355</v>
       </c>
       <c r="C28">
-        <v>323.3861487112062</v>
+        <v>309.3845426643826</v>
       </c>
       <c r="D28">
-        <v>410.0141487112062</v>
+        <v>400.2405426643826</v>
       </c>
       <c r="E28">
-        <v>12.328</v>
+        <v>16.556</v>
       </c>
       <c r="F28">
-        <v>109.928</v>
+        <v>114.156</v>
       </c>
       <c r="G28">
         <v>23.3</v>
@@ -3583,45 +3583,45 @@
         <v>21.8</v>
       </c>
       <c r="M28">
-        <v>7.0463848</v>
+        <v>8.2078164</v>
       </c>
       <c r="N28">
-        <v>14.7536152</v>
+        <v>13.5921836</v>
       </c>
       <c r="O28">
-        <v>2.360578432</v>
+        <v>2.174749376</v>
       </c>
       <c r="P28">
-        <v>12.393036768</v>
+        <v>11.417434224</v>
       </c>
       <c r="Q28">
-        <v>34.693036768</v>
+        <v>33.717434224</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1252577066277172</v>
+        <v>0.1262117006355281</v>
       </c>
       <c r="T28">
-        <v>1.093765240007224</v>
+        <v>1.10689732661284</v>
       </c>
       <c r="U28">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V28">
         <v>0.16</v>
       </c>
       <c r="W28">
-        <v>0.053844</v>
+        <v>0.06039600000000001</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y28">
-        <v>3.093785056984115</v>
+        <v>2.656004829737663</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1084414614639355</v>
+        <v>0.1084892600233604</v>
       </c>
       <c r="C29">
-        <v>309.3845426643826</v>
+        <v>304.8963205101491</v>
       </c>
       <c r="D29">
-        <v>400.2405426643826</v>
+        <v>399.9803205101491</v>
       </c>
       <c r="E29">
-        <v>16.556</v>
+        <v>20.78400000000001</v>
       </c>
       <c r="F29">
-        <v>114.156</v>
+        <v>118.384</v>
       </c>
       <c r="G29">
         <v>23.3</v>
@@ -3665,28 +3665,28 @@
         <v>21.8</v>
       </c>
       <c r="M29">
-        <v>8.2078164</v>
+        <v>8.511809600000001</v>
       </c>
       <c r="N29">
-        <v>13.5921836</v>
+        <v>13.2881904</v>
       </c>
       <c r="O29">
-        <v>2.174749376</v>
+        <v>2.126110464</v>
       </c>
       <c r="P29">
-        <v>11.417434224</v>
+        <v>11.162079936</v>
       </c>
       <c r="Q29">
-        <v>33.717434224</v>
+        <v>33.462079936</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1262117006355281</v>
+        <v>0.1271921944768894</v>
       </c>
       <c r="T29">
-        <v>1.10689732661284</v>
+        <v>1.120394193401946</v>
       </c>
       <c r="U29">
         <v>0.07190000000000001</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>2.656004829737663</v>
+        <v>2.561147514389889</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1084892600233604</v>
+        <v>0.1094870985827852</v>
       </c>
       <c r="C30">
-        <v>304.8963205101491</v>
+        <v>295.3121751991717</v>
       </c>
       <c r="D30">
-        <v>399.9803205101491</v>
+        <v>394.6241751991718</v>
       </c>
       <c r="E30">
-        <v>20.78400000000001</v>
+        <v>25.012</v>
       </c>
       <c r="F30">
-        <v>118.384</v>
+        <v>122.612</v>
       </c>
       <c r="G30">
         <v>23.3</v>
@@ -3747,45 +3747,45 @@
         <v>21.8</v>
       </c>
       <c r="M30">
-        <v>8.511809600000001</v>
+        <v>9.2939896</v>
       </c>
       <c r="N30">
-        <v>13.2881904</v>
+        <v>12.5060104</v>
       </c>
       <c r="O30">
-        <v>2.126110464</v>
+        <v>2.000961664</v>
       </c>
       <c r="P30">
-        <v>11.162079936</v>
+        <v>10.505048736</v>
       </c>
       <c r="Q30">
-        <v>33.462079936</v>
+        <v>32.805048736</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1271921944768894</v>
+        <v>0.1282003078630778</v>
       </c>
       <c r="T30">
-        <v>1.120394193401946</v>
+        <v>1.134271253621731</v>
       </c>
       <c r="U30">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V30">
         <v>0.16</v>
       </c>
       <c r="W30">
-        <v>0.06039600000000001</v>
+        <v>0.06367200000000001</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y30">
-        <v>2.561147514389889</v>
+        <v>2.345601936115788</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1094870985827852</v>
+        <v>0.1095676571422101</v>
       </c>
       <c r="C31">
-        <v>295.3121751991718</v>
+        <v>290.6580084500853</v>
       </c>
       <c r="D31">
-        <v>394.6241751991718</v>
+        <v>394.1980084500853</v>
       </c>
       <c r="E31">
-        <v>25.01199999999999</v>
+        <v>29.23999999999998</v>
       </c>
       <c r="F31">
-        <v>122.612</v>
+        <v>126.84</v>
       </c>
       <c r="G31">
         <v>23.3</v>
@@ -3829,28 +3829,28 @@
         <v>21.8</v>
       </c>
       <c r="M31">
-        <v>9.2939896</v>
+        <v>9.614471999999999</v>
       </c>
       <c r="N31">
-        <v>12.5060104</v>
+        <v>12.185528</v>
       </c>
       <c r="O31">
-        <v>2.000961664</v>
+        <v>1.94968448</v>
       </c>
       <c r="P31">
-        <v>10.505048736</v>
+        <v>10.23584352</v>
       </c>
       <c r="Q31">
-        <v>32.805048736</v>
+        <v>32.53584352</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1282003078630778</v>
+        <v>0.1292372244888716</v>
       </c>
       <c r="T31">
-        <v>1.134271253621731</v>
+        <v>1.148544801276366</v>
       </c>
       <c r="U31">
         <v>0.07580000000000001</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.345601936115788</v>
+        <v>2.267415204911929</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1095676571422101</v>
+        <v>0.109648215701635</v>
       </c>
       <c r="C32">
-        <v>290.6580084500853</v>
+        <v>286.0047611691209</v>
       </c>
       <c r="D32">
-        <v>394.1980084500853</v>
+        <v>393.7727611691208</v>
       </c>
       <c r="E32">
-        <v>29.23999999999998</v>
+        <v>33.46799999999999</v>
       </c>
       <c r="F32">
-        <v>126.84</v>
+        <v>131.068</v>
       </c>
       <c r="G32">
         <v>23.3</v>
@@ -3911,28 +3911,28 @@
         <v>21.8</v>
       </c>
       <c r="M32">
-        <v>9.614471999999999</v>
+        <v>9.934954399999999</v>
       </c>
       <c r="N32">
-        <v>12.185528</v>
+        <v>11.8650456</v>
       </c>
       <c r="O32">
-        <v>1.94968448</v>
+        <v>1.898407296</v>
       </c>
       <c r="P32">
-        <v>10.23584352</v>
+        <v>9.966638304000002</v>
       </c>
       <c r="Q32">
-        <v>32.53584352</v>
+        <v>32.266638304</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1292372244888716</v>
+        <v>0.1303041966690362</v>
       </c>
       <c r="T32">
-        <v>1.148544801276366</v>
+        <v>1.163232074949977</v>
       </c>
       <c r="U32">
         <v>0.07580000000000001</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>2.267415204911929</v>
+        <v>2.194272778947028</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.109648215701635</v>
+        <v>0.1097287742610598</v>
       </c>
       <c r="C33">
-        <v>286.0047611691209</v>
+        <v>281.3524303838134</v>
       </c>
       <c r="D33">
-        <v>393.7727611691208</v>
+        <v>393.3484303838134</v>
       </c>
       <c r="E33">
-        <v>33.46799999999999</v>
+        <v>37.696</v>
       </c>
       <c r="F33">
-        <v>131.068</v>
+        <v>135.296</v>
       </c>
       <c r="G33">
         <v>23.3</v>
@@ -3993,28 +3993,28 @@
         <v>21.8</v>
       </c>
       <c r="M33">
-        <v>9.934954399999999</v>
+        <v>10.2554368</v>
       </c>
       <c r="N33">
-        <v>11.8650456</v>
+        <v>11.5445632</v>
       </c>
       <c r="O33">
-        <v>1.898407296</v>
+        <v>1.847130112</v>
       </c>
       <c r="P33">
-        <v>9.966638304000002</v>
+        <v>9.697433088</v>
       </c>
       <c r="Q33">
-        <v>32.266638304</v>
+        <v>31.997433088</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1303041966690362</v>
+        <v>0.1314025503839115</v>
       </c>
       <c r="T33">
-        <v>1.163232074949977</v>
+        <v>1.178351327261047</v>
       </c>
       <c r="U33">
         <v>0.07580000000000001</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.194272778947028</v>
+        <v>2.125701754604933</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1097287742610598</v>
+        <v>0.1098093328204847</v>
       </c>
       <c r="C34">
-        <v>281.3524303838134</v>
+        <v>276.7010131344958</v>
       </c>
       <c r="D34">
-        <v>393.3484303838134</v>
+        <v>392.9250131344958</v>
       </c>
       <c r="E34">
-        <v>37.696</v>
+        <v>41.92400000000001</v>
       </c>
       <c r="F34">
-        <v>135.296</v>
+        <v>139.524</v>
       </c>
       <c r="G34">
         <v>23.3</v>
@@ -4075,28 +4075,28 @@
         <v>21.8</v>
       </c>
       <c r="M34">
-        <v>10.2554368</v>
+        <v>10.5759192</v>
       </c>
       <c r="N34">
-        <v>11.5445632</v>
+        <v>11.2240808</v>
       </c>
       <c r="O34">
-        <v>1.847130112</v>
+        <v>1.795852928</v>
       </c>
       <c r="P34">
-        <v>9.697433088</v>
+        <v>9.428227871999999</v>
       </c>
       <c r="Q34">
-        <v>31.997433088</v>
+        <v>31.728227872</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1314025503839115</v>
+        <v>0.1325336907768428</v>
       </c>
       <c r="T34">
-        <v>1.178351327261047</v>
+        <v>1.193921900536627</v>
       </c>
       <c r="U34">
         <v>0.07580000000000001</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.125701754604933</v>
+        <v>2.061286549919935</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1098093328204847</v>
+        <v>0.1098898913799095</v>
       </c>
       <c r="C35">
-        <v>276.7010131344958</v>
+        <v>272.0505064742321</v>
       </c>
       <c r="D35">
-        <v>392.9250131344958</v>
+        <v>392.5025064742321</v>
       </c>
       <c r="E35">
-        <v>41.92400000000001</v>
+        <v>46.15199999999999</v>
       </c>
       <c r="F35">
-        <v>139.524</v>
+        <v>143.752</v>
       </c>
       <c r="G35">
         <v>23.3</v>
@@ -4157,28 +4157,28 @@
         <v>21.8</v>
       </c>
       <c r="M35">
-        <v>10.5759192</v>
+        <v>10.8964016</v>
       </c>
       <c r="N35">
-        <v>11.2240808</v>
+        <v>10.9035984</v>
       </c>
       <c r="O35">
-        <v>1.795852928</v>
+        <v>1.744575744</v>
       </c>
       <c r="P35">
-        <v>9.428227871999999</v>
+        <v>9.159022656000001</v>
       </c>
       <c r="Q35">
-        <v>31.728227872</v>
+        <v>31.459022656</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1325336907768428</v>
+        <v>0.1336991081513781</v>
       </c>
       <c r="T35">
-        <v>1.193921900536627</v>
+        <v>1.209964309366012</v>
       </c>
       <c r="U35">
         <v>0.07580000000000001</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.061286549919935</v>
+        <v>2.00066047492229</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1098898913799095</v>
+        <v>0.1141452499393344</v>
       </c>
       <c r="C36">
-        <v>272.0505064742321</v>
+        <v>246.72661024244</v>
       </c>
       <c r="D36">
-        <v>392.5025064742321</v>
+        <v>371.40661024244</v>
       </c>
       <c r="E36">
-        <v>46.15199999999999</v>
+        <v>50.38</v>
       </c>
       <c r="F36">
-        <v>143.752</v>
+        <v>147.98</v>
       </c>
       <c r="G36">
         <v>23.3</v>
@@ -4239,45 +4239,45 @@
         <v>21.8</v>
       </c>
       <c r="M36">
-        <v>10.8964016</v>
+        <v>13.3182</v>
       </c>
       <c r="N36">
-        <v>10.9035984</v>
+        <v>8.481800000000002</v>
       </c>
       <c r="O36">
-        <v>1.744575744</v>
+        <v>1.357088</v>
       </c>
       <c r="P36">
-        <v>9.159022656000001</v>
+        <v>7.124712000000001</v>
       </c>
       <c r="Q36">
-        <v>31.459022656</v>
+        <v>29.424712</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1336991081513781</v>
+        <v>0.1349003845220529</v>
       </c>
       <c r="T36">
-        <v>1.209964309366012</v>
+        <v>1.226500330774762</v>
       </c>
       <c r="U36">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V36">
         <v>0.16</v>
       </c>
       <c r="W36">
-        <v>0.06367200000000001</v>
+        <v>0.0756</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y36">
-        <v>2.00066047492229</v>
+        <v>1.636857833641183</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1141452499393344</v>
+        <v>0.1143450884987592</v>
       </c>
       <c r="C37">
-        <v>246.72661024244</v>
+        <v>241.5635200460934</v>
       </c>
       <c r="D37">
-        <v>371.40661024244</v>
+        <v>370.4715200460934</v>
       </c>
       <c r="E37">
-        <v>50.38</v>
+        <v>54.608</v>
       </c>
       <c r="F37">
-        <v>147.98</v>
+        <v>152.208</v>
       </c>
       <c r="G37">
         <v>23.3</v>
@@ -4321,28 +4321,28 @@
         <v>21.8</v>
       </c>
       <c r="M37">
-        <v>13.3182</v>
+        <v>13.69872</v>
       </c>
       <c r="N37">
-        <v>8.481800000000002</v>
+        <v>8.101280000000001</v>
       </c>
       <c r="O37">
-        <v>1.357088</v>
+        <v>1.2962048</v>
       </c>
       <c r="P37">
-        <v>7.124712000000001</v>
+        <v>6.805075200000001</v>
       </c>
       <c r="Q37">
-        <v>29.424712</v>
+        <v>29.1050752</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1349003845220529</v>
+        <v>0.1361392007793113</v>
       </c>
       <c r="T37">
-        <v>1.226500330774762</v>
+        <v>1.243553102852537</v>
       </c>
       <c r="U37">
         <v>0.09</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>1.636857833641183</v>
+        <v>1.591389560484483</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1143450884987593</v>
+        <v>0.1145449270581841</v>
       </c>
       <c r="C38">
-        <v>241.5635200460933</v>
+        <v>236.405126576835</v>
       </c>
       <c r="D38">
-        <v>370.4715200460933</v>
+        <v>369.541126576835</v>
       </c>
       <c r="E38">
-        <v>54.60799999999998</v>
+        <v>58.83599999999998</v>
       </c>
       <c r="F38">
-        <v>152.208</v>
+        <v>156.436</v>
       </c>
       <c r="G38">
         <v>23.3</v>
@@ -4403,28 +4403,28 @@
         <v>21.8</v>
       </c>
       <c r="M38">
-        <v>13.69872</v>
+        <v>14.07924</v>
       </c>
       <c r="N38">
-        <v>8.101280000000004</v>
+        <v>7.720760000000004</v>
       </c>
       <c r="O38">
-        <v>1.296204800000001</v>
+        <v>1.235321600000001</v>
       </c>
       <c r="P38">
-        <v>6.805075200000004</v>
+        <v>6.485438400000003</v>
       </c>
       <c r="Q38">
-        <v>29.10507520000001</v>
+        <v>28.7854384</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1361392007793113</v>
+        <v>0.1374173445368002</v>
       </c>
       <c r="T38">
-        <v>1.243553102852536</v>
+        <v>1.26114723277405</v>
       </c>
       <c r="U38">
         <v>0.09</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>1.591389560484484</v>
+        <v>1.548379031822741</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1145449270581841</v>
+        <v>0.114744765617609</v>
       </c>
       <c r="C39">
-        <v>236.405126576835</v>
+        <v>231.2513945375595</v>
       </c>
       <c r="D39">
-        <v>369.541126576835</v>
+        <v>368.6153945375594</v>
       </c>
       <c r="E39">
-        <v>58.83599999999998</v>
+        <v>63.06399999999999</v>
       </c>
       <c r="F39">
-        <v>156.436</v>
+        <v>160.664</v>
       </c>
       <c r="G39">
         <v>23.3</v>
@@ -4485,28 +4485,28 @@
         <v>21.8</v>
       </c>
       <c r="M39">
-        <v>14.07924</v>
+        <v>14.45976</v>
       </c>
       <c r="N39">
-        <v>7.720760000000004</v>
+        <v>7.340240000000003</v>
       </c>
       <c r="O39">
-        <v>1.235321600000001</v>
+        <v>1.174438400000001</v>
       </c>
       <c r="P39">
-        <v>6.485438400000003</v>
+        <v>6.165801600000003</v>
       </c>
       <c r="Q39">
-        <v>28.7854384</v>
+        <v>28.4658016</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1374173445368002</v>
+        <v>0.138736718738079</v>
       </c>
       <c r="T39">
-        <v>1.26114723277405</v>
+        <v>1.279308915273676</v>
       </c>
       <c r="U39">
         <v>0.09</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>1.548379031822741</v>
+        <v>1.507632215195827</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.114744765617609</v>
+        <v>0.1348433819913609</v>
       </c>
       <c r="C40">
-        <v>231.2513945375595</v>
+        <v>152.8416790419902</v>
       </c>
       <c r="D40">
-        <v>368.6153945375594</v>
+        <v>294.4336790419902</v>
       </c>
       <c r="E40">
-        <v>63.06399999999999</v>
+        <v>67.292</v>
       </c>
       <c r="F40">
-        <v>160.664</v>
+        <v>164.892</v>
       </c>
       <c r="G40">
         <v>23.3</v>
@@ -4567,45 +4567,45 @@
         <v>21.8</v>
       </c>
       <c r="M40">
-        <v>14.45976</v>
+        <v>24.2061456</v>
       </c>
       <c r="N40">
-        <v>7.340240000000003</v>
+        <v>-2.406145600000002</v>
       </c>
       <c r="O40">
-        <v>1.174438400000001</v>
+        <v>-0.3849832960000004</v>
       </c>
       <c r="P40">
-        <v>6.165801600000003</v>
+        <v>-2.021162304000002</v>
       </c>
       <c r="Q40">
-        <v>28.4658016</v>
+        <v>20.278837696</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.138736718738079</v>
+        <v>0.1407231892998566</v>
       </c>
       <c r="T40">
-        <v>1.279308915273676</v>
+        <v>1.306653430273962</v>
       </c>
       <c r="U40">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V40">
-        <v>0.16</v>
+        <v>0.1440956382580794</v>
       </c>
       <c r="W40">
-        <v>0.0756</v>
+        <v>0.125646760303714</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y40">
-        <v>1.507632215195827</v>
+        <v>0.9005977391129961</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1348433819913609</v>
+        <v>0.135853381991361</v>
       </c>
       <c r="C41">
-        <v>152.8416790419902</v>
+        <v>145.6658916584518</v>
       </c>
       <c r="D41">
-        <v>294.4336790419902</v>
+        <v>291.4858916584517</v>
       </c>
       <c r="E41">
-        <v>67.292</v>
+        <v>71.52000000000001</v>
       </c>
       <c r="F41">
-        <v>164.892</v>
+        <v>169.12</v>
       </c>
       <c r="G41">
         <v>23.3</v>
@@ -4649,37 +4649,37 @@
         <v>21.8</v>
       </c>
       <c r="M41">
-        <v>24.2061456</v>
+        <v>24.826816</v>
       </c>
       <c r="N41">
-        <v>-2.406145600000002</v>
+        <v>-3.026816000000004</v>
       </c>
       <c r="O41">
-        <v>-0.3849832960000004</v>
+        <v>-0.4842905600000006</v>
       </c>
       <c r="P41">
-        <v>-2.021162304000002</v>
+        <v>-2.542525440000003</v>
       </c>
       <c r="Q41">
-        <v>20.278837696</v>
+        <v>19.75747456</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1407231892998566</v>
+        <v>0.1423052424548542</v>
       </c>
       <c r="T41">
-        <v>1.306653430273962</v>
+        <v>1.328430987445195</v>
       </c>
       <c r="U41">
         <v>0.1468</v>
       </c>
       <c r="V41">
-        <v>0.1440956382580794</v>
+        <v>0.1404932473016274</v>
       </c>
       <c r="W41">
-        <v>0.125646760303714</v>
+        <v>0.1261755912961211</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.9005977391129961</v>
+        <v>0.8780827956351711</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.135853381991361</v>
+        <v>0.1368633819913609</v>
       </c>
       <c r="C42">
-        <v>145.6658916584518</v>
+        <v>138.5485440328647</v>
       </c>
       <c r="D42">
-        <v>291.4858916584517</v>
+        <v>288.5965440328646</v>
       </c>
       <c r="E42">
-        <v>71.52000000000001</v>
+        <v>75.74799999999999</v>
       </c>
       <c r="F42">
-        <v>169.12</v>
+        <v>173.348</v>
       </c>
       <c r="G42">
         <v>23.3</v>
@@ -4731,37 +4731,37 @@
         <v>21.8</v>
       </c>
       <c r="M42">
-        <v>24.826816</v>
+        <v>25.4474864</v>
       </c>
       <c r="N42">
-        <v>-3.026816000000004</v>
+        <v>-3.647486399999998</v>
       </c>
       <c r="O42">
-        <v>-0.4842905600000006</v>
+        <v>-0.5835978239999997</v>
       </c>
       <c r="P42">
-        <v>-2.542525440000003</v>
+        <v>-3.063888575999998</v>
       </c>
       <c r="Q42">
-        <v>19.75747456</v>
+        <v>19.236111424</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1423052424548542</v>
+        <v>0.1439409245303602</v>
       </c>
       <c r="T42">
-        <v>1.328430987445195</v>
+        <v>1.350946766893418</v>
       </c>
       <c r="U42">
         <v>0.1468</v>
       </c>
       <c r="V42">
-        <v>0.1404932473016274</v>
+        <v>0.1370665827332951</v>
       </c>
       <c r="W42">
-        <v>0.1261755912961211</v>
+        <v>0.1266786256547523</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.8780827956351711</v>
+        <v>0.856666142083094</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1368633819913609</v>
+        <v>0.137873381991361</v>
       </c>
       <c r="C43">
-        <v>138.5485440328647</v>
+        <v>131.4879153740071</v>
       </c>
       <c r="D43">
-        <v>288.5965440328646</v>
+        <v>285.7639153740071</v>
       </c>
       <c r="E43">
-        <v>75.74799999999999</v>
+        <v>79.976</v>
       </c>
       <c r="F43">
-        <v>173.348</v>
+        <v>177.576</v>
       </c>
       <c r="G43">
         <v>23.3</v>
@@ -4813,37 +4813,37 @@
         <v>21.8</v>
       </c>
       <c r="M43">
-        <v>25.4474864</v>
+        <v>26.0681568</v>
       </c>
       <c r="N43">
-        <v>-3.647486399999998</v>
+        <v>-4.2681568</v>
       </c>
       <c r="O43">
-        <v>-0.5835978239999997</v>
+        <v>-0.6829050879999999</v>
       </c>
       <c r="P43">
-        <v>-3.063888575999998</v>
+        <v>-3.585251712</v>
       </c>
       <c r="Q43">
-        <v>19.236111424</v>
+        <v>18.714748288</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1439409245303602</v>
+        <v>0.1456330094360561</v>
       </c>
       <c r="T43">
-        <v>1.350946766893418</v>
+        <v>1.374238952529512</v>
       </c>
       <c r="U43">
         <v>0.1468</v>
       </c>
       <c r="V43">
-        <v>0.1370665827332951</v>
+        <v>0.1338030926682166</v>
       </c>
       <c r="W43">
-        <v>0.1266786256547523</v>
+        <v>0.1271577059963058</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.856666142083094</v>
+        <v>0.8362693291763535</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.137873381991361</v>
+        <v>0.138883381991361</v>
       </c>
       <c r="C44">
-        <v>131.4879153740071</v>
+        <v>124.4823517935346</v>
       </c>
       <c r="D44">
-        <v>285.7639153740071</v>
+        <v>282.9863517935345</v>
       </c>
       <c r="E44">
-        <v>79.97599999999997</v>
+        <v>84.20399999999998</v>
       </c>
       <c r="F44">
-        <v>177.576</v>
+        <v>181.804</v>
       </c>
       <c r="G44">
         <v>23.3</v>
@@ -4895,37 +4895,37 @@
         <v>21.8</v>
       </c>
       <c r="M44">
-        <v>26.0681568</v>
+        <v>26.6888272</v>
       </c>
       <c r="N44">
-        <v>-4.268156799999996</v>
+        <v>-4.888827199999998</v>
       </c>
       <c r="O44">
-        <v>-0.6829050879999994</v>
+        <v>-0.7822123519999997</v>
       </c>
       <c r="P44">
-        <v>-3.585251711999997</v>
+        <v>-4.106614847999998</v>
       </c>
       <c r="Q44">
-        <v>18.714748288</v>
+        <v>18.193385152</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1456330094360561</v>
+        <v>0.1473844657419518</v>
       </c>
       <c r="T44">
-        <v>1.374238952529512</v>
+        <v>1.398348407837047</v>
       </c>
       <c r="U44">
         <v>0.1468</v>
       </c>
       <c r="V44">
-        <v>0.1338030926682166</v>
+        <v>0.1306913928387232</v>
       </c>
       <c r="W44">
-        <v>0.1271577059963058</v>
+        <v>0.1276145035312754</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.8362693291763537</v>
+        <v>0.8168212052420198</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.138883381991361</v>
+        <v>0.1645805670704138</v>
       </c>
       <c r="C45">
-        <v>124.4823517935346</v>
+        <v>64.14748387484866</v>
       </c>
       <c r="D45">
-        <v>282.9863517935345</v>
+        <v>226.8794838748486</v>
       </c>
       <c r="E45">
-        <v>84.20399999999998</v>
+        <v>88.43199999999999</v>
       </c>
       <c r="F45">
-        <v>181.804</v>
+        <v>186.032</v>
       </c>
       <c r="G45">
         <v>23.3</v>
@@ -4977,45 +4977,45 @@
         <v>21.8</v>
       </c>
       <c r="M45">
-        <v>26.6888272</v>
+        <v>37.3552256</v>
       </c>
       <c r="N45">
-        <v>-4.888827199999998</v>
+        <v>-15.5552256</v>
       </c>
       <c r="O45">
-        <v>-0.7822123519999997</v>
+        <v>-2.488836096</v>
       </c>
       <c r="P45">
-        <v>-4.106614847999998</v>
+        <v>-13.066389504</v>
       </c>
       <c r="Q45">
-        <v>18.193385152</v>
+        <v>9.233610496000004</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1473844657419518</v>
+        <v>0.1508541616999381</v>
       </c>
       <c r="T45">
-        <v>1.398348407837047</v>
+        <v>1.446110078709576</v>
       </c>
       <c r="U45">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.1306913928387232</v>
+        <v>0.09337381702226959</v>
       </c>
       <c r="W45">
-        <v>0.1276145035312754</v>
+        <v>0.1820505375419283</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y45">
-        <v>0.8168212052420198</v>
+        <v>0.5835863563891849</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1645805670704138</v>
+        <v>0.1661305670704137</v>
       </c>
       <c r="C46">
-        <v>64.14748387484866</v>
+        <v>57.23828537468151</v>
       </c>
       <c r="D46">
-        <v>226.8794838748486</v>
+        <v>224.1982853746815</v>
       </c>
       <c r="E46">
-        <v>88.43199999999999</v>
+        <v>92.66</v>
       </c>
       <c r="F46">
-        <v>186.032</v>
+        <v>190.26</v>
       </c>
       <c r="G46">
         <v>23.3</v>
@@ -5059,37 +5059,37 @@
         <v>21.8</v>
       </c>
       <c r="M46">
-        <v>37.3552256</v>
+        <v>38.204208</v>
       </c>
       <c r="N46">
-        <v>-15.5552256</v>
+        <v>-16.404208</v>
       </c>
       <c r="O46">
-        <v>-2.488836096</v>
+        <v>-2.62467328</v>
       </c>
       <c r="P46">
-        <v>-13.066389504</v>
+        <v>-13.77953472</v>
       </c>
       <c r="Q46">
-        <v>9.233610496000004</v>
+        <v>8.52046528</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1508541616999381</v>
+        <v>0.1527642373672096</v>
       </c>
       <c r="T46">
-        <v>1.446110078709576</v>
+        <v>1.472402989231568</v>
       </c>
       <c r="U46">
         <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.09337381702226959</v>
+        <v>0.09129884331066357</v>
       </c>
       <c r="W46">
-        <v>0.1820505375419283</v>
+        <v>0.1824671922632188</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.5835863563891849</v>
+        <v>0.5706177706916473</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1661305670704137</v>
+        <v>0.1676805670704138</v>
       </c>
       <c r="C47">
-        <v>57.23828537468151</v>
+        <v>50.39171803001463</v>
       </c>
       <c r="D47">
-        <v>224.1982853746815</v>
+        <v>221.5797180300146</v>
       </c>
       <c r="E47">
-        <v>92.66</v>
+        <v>96.88800000000001</v>
       </c>
       <c r="F47">
-        <v>190.26</v>
+        <v>194.488</v>
       </c>
       <c r="G47">
         <v>23.3</v>
@@ -5141,37 +5141,37 @@
         <v>21.8</v>
       </c>
       <c r="M47">
-        <v>38.204208</v>
+        <v>39.0531904</v>
       </c>
       <c r="N47">
-        <v>-16.404208</v>
+        <v>-17.2531904</v>
       </c>
       <c r="O47">
-        <v>-2.62467328</v>
+        <v>-2.760510464</v>
       </c>
       <c r="P47">
-        <v>-13.77953472</v>
+        <v>-14.492679936</v>
       </c>
       <c r="Q47">
-        <v>8.52046528</v>
+        <v>7.807320064000002</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1527642373672096</v>
+        <v>0.1547450565777135</v>
       </c>
       <c r="T47">
-        <v>1.472402989231568</v>
+        <v>1.499669711254375</v>
       </c>
       <c r="U47">
         <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.09129884331066357</v>
+        <v>0.0893140858473883</v>
       </c>
       <c r="W47">
-        <v>0.1824671922632188</v>
+        <v>0.1828657315618444</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.5706177706916473</v>
+        <v>0.5582130365461768</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1676805670704138</v>
+        <v>0.1692305670704138</v>
       </c>
       <c r="C48">
-        <v>50.39171803001463</v>
+        <v>43.60561263829661</v>
       </c>
       <c r="D48">
-        <v>221.5797180300146</v>
+        <v>219.0216126382966</v>
       </c>
       <c r="E48">
-        <v>96.88800000000001</v>
+        <v>101.116</v>
       </c>
       <c r="F48">
-        <v>194.488</v>
+        <v>198.716</v>
       </c>
       <c r="G48">
         <v>23.3</v>
@@ -5223,37 +5223,37 @@
         <v>21.8</v>
       </c>
       <c r="M48">
-        <v>39.0531904</v>
+        <v>39.9021728</v>
       </c>
       <c r="N48">
-        <v>-17.2531904</v>
+        <v>-18.10217279999999</v>
       </c>
       <c r="O48">
-        <v>-2.760510464</v>
+        <v>-2.896347647999999</v>
       </c>
       <c r="P48">
-        <v>-14.492679936</v>
+        <v>-15.205825152</v>
       </c>
       <c r="Q48">
-        <v>7.807320064000002</v>
+        <v>7.094174848000005</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1547450565777135</v>
+        <v>0.1568006236829534</v>
       </c>
       <c r="T48">
-        <v>1.499669711254375</v>
+        <v>1.527965366183703</v>
       </c>
       <c r="U48">
         <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.0893140858473883</v>
+        <v>0.0874137861485077</v>
       </c>
       <c r="W48">
-        <v>0.1828657315618444</v>
+        <v>0.1832473117413796</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.5582130365461768</v>
+        <v>0.5463361634281731</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1692305670704138</v>
+        <v>0.1707805670704138</v>
       </c>
       <c r="C49">
-        <v>43.60561263829661</v>
+        <v>36.87789902620088</v>
       </c>
       <c r="D49">
-        <v>219.0216126382966</v>
+        <v>216.5218990262009</v>
       </c>
       <c r="E49">
-        <v>101.116</v>
+        <v>105.344</v>
       </c>
       <c r="F49">
-        <v>198.716</v>
+        <v>202.944</v>
       </c>
       <c r="G49">
         <v>23.3</v>
@@ -5305,37 +5305,37 @@
         <v>21.8</v>
       </c>
       <c r="M49">
-        <v>39.9021728</v>
+        <v>40.7511552</v>
       </c>
       <c r="N49">
-        <v>-18.10217279999999</v>
+        <v>-18.9511552</v>
       </c>
       <c r="O49">
-        <v>-2.896347647999999</v>
+        <v>-3.032184832</v>
       </c>
       <c r="P49">
-        <v>-15.205825152</v>
+        <v>-15.918970368</v>
       </c>
       <c r="Q49">
-        <v>7.094174848000005</v>
+        <v>6.381029632000002</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1568006236829534</v>
+        <v>0.1589352510614717</v>
       </c>
       <c r="T49">
-        <v>1.527965366183703</v>
+        <v>1.557349315533389</v>
       </c>
       <c r="U49">
         <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.0874137861485077</v>
+        <v>0.08559266560374711</v>
       </c>
       <c r="W49">
-        <v>0.1832473117413796</v>
+        <v>0.1836129927467676</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.5463361634281731</v>
+        <v>0.5349541600234194</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1707805670704138</v>
+        <v>0.1723305670704137</v>
       </c>
       <c r="C50">
-        <v>36.87789902620091</v>
+        <v>30.20660046224765</v>
       </c>
       <c r="D50">
-        <v>216.5218990262009</v>
+        <v>214.0786004622476</v>
       </c>
       <c r="E50">
-        <v>105.344</v>
+        <v>109.572</v>
       </c>
       <c r="F50">
-        <v>202.944</v>
+        <v>207.172</v>
       </c>
       <c r="G50">
         <v>23.3</v>
@@ -5387,37 +5387,37 @@
         <v>21.8</v>
       </c>
       <c r="M50">
-        <v>40.75115519999999</v>
+        <v>41.6001376</v>
       </c>
       <c r="N50">
-        <v>-18.95115519999999</v>
+        <v>-19.8001376</v>
       </c>
       <c r="O50">
-        <v>-3.032184831999999</v>
+        <v>-3.168022015999999</v>
       </c>
       <c r="P50">
-        <v>-15.91897036799999</v>
+        <v>-16.632115584</v>
       </c>
       <c r="Q50">
-        <v>6.381029632000008</v>
+        <v>5.667884416000003</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1589352510614717</v>
+        <v>0.161153589317579</v>
       </c>
       <c r="T50">
-        <v>1.557349315533389</v>
+        <v>1.587885576622279</v>
       </c>
       <c r="U50">
         <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.08559266560374713</v>
+        <v>0.0838458765097931</v>
       </c>
       <c r="W50">
-        <v>0.1836129927467676</v>
+        <v>0.1839637479968335</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.5349541600234196</v>
+        <v>0.5240367281862068</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1723305670704137</v>
+        <v>0.1738805670704138</v>
       </c>
       <c r="C51">
-        <v>30.20660046224765</v>
+        <v>23.58982844350172</v>
       </c>
       <c r="D51">
-        <v>214.0786004622476</v>
+        <v>211.6898284435017</v>
       </c>
       <c r="E51">
-        <v>109.572</v>
+        <v>113.8</v>
       </c>
       <c r="F51">
-        <v>207.172</v>
+        <v>211.4</v>
       </c>
       <c r="G51">
         <v>23.3</v>
@@ -5469,37 +5469,37 @@
         <v>21.8</v>
       </c>
       <c r="M51">
-        <v>41.6001376</v>
+        <v>42.44911999999999</v>
       </c>
       <c r="N51">
-        <v>-19.8001376</v>
+        <v>-20.64911999999999</v>
       </c>
       <c r="O51">
-        <v>-3.168022015999999</v>
+        <v>-3.303859199999999</v>
       </c>
       <c r="P51">
-        <v>-16.632115584</v>
+        <v>-17.34526079999999</v>
       </c>
       <c r="Q51">
-        <v>5.667884416000003</v>
+        <v>4.954739200000006</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.161153589317579</v>
+        <v>0.1634606611039306</v>
       </c>
       <c r="T51">
-        <v>1.587885576622279</v>
+        <v>1.619643288154725</v>
       </c>
       <c r="U51">
         <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.0838458765097931</v>
+        <v>0.08216895897959724</v>
       </c>
       <c r="W51">
-        <v>0.1839637479968335</v>
+        <v>0.1843004730368969</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.5240367281862068</v>
+        <v>0.5135559936224827</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1738805670704138</v>
+        <v>0.1754305670704138</v>
       </c>
       <c r="C52">
-        <v>23.58982844350172</v>
+        <v>17.02577782745166</v>
       </c>
       <c r="D52">
-        <v>211.6898284435017</v>
+        <v>209.3537778274516</v>
       </c>
       <c r="E52">
-        <v>113.8</v>
+        <v>118.028</v>
       </c>
       <c r="F52">
-        <v>211.4</v>
+        <v>215.628</v>
       </c>
       <c r="G52">
         <v>23.3</v>
@@ -5551,37 +5551,37 @@
         <v>21.8</v>
       </c>
       <c r="M52">
-        <v>42.44911999999999</v>
+        <v>43.2981024</v>
       </c>
       <c r="N52">
-        <v>-20.64911999999999</v>
+        <v>-21.4981024</v>
       </c>
       <c r="O52">
-        <v>-3.303859199999999</v>
+        <v>-3.439696383999999</v>
       </c>
       <c r="P52">
-        <v>-17.34526079999999</v>
+        <v>-18.058406016</v>
       </c>
       <c r="Q52">
-        <v>4.954739200000006</v>
+        <v>4.241593984000001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1634606611039306</v>
+        <v>0.1658618990856435</v>
       </c>
       <c r="T52">
-        <v>1.619643288154725</v>
+        <v>1.652697232810944</v>
       </c>
       <c r="U52">
         <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.08216895897959724</v>
+        <v>0.08055780292117376</v>
       </c>
       <c r="W52">
-        <v>0.1843004730368969</v>
+        <v>0.1846239931734283</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.5135559936224827</v>
+        <v>0.503486268257336</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1754305670704138</v>
+        <v>0.1955546974489654</v>
       </c>
       <c r="C53">
-        <v>17.02577782745166</v>
+        <v>-13.43825223734504</v>
       </c>
       <c r="D53">
-        <v>209.3537778274516</v>
+        <v>183.1177477626549</v>
       </c>
       <c r="E53">
-        <v>118.028</v>
+        <v>122.256</v>
       </c>
       <c r="F53">
-        <v>215.628</v>
+        <v>219.856</v>
       </c>
       <c r="G53">
         <v>23.3</v>
@@ -5633,45 +5633,45 @@
         <v>21.8</v>
       </c>
       <c r="M53">
-        <v>43.2981024</v>
+        <v>51.8420448</v>
       </c>
       <c r="N53">
-        <v>-21.4981024</v>
+        <v>-30.0420448</v>
       </c>
       <c r="O53">
-        <v>-3.439696383999999</v>
+        <v>-4.806727168000001</v>
       </c>
       <c r="P53">
-        <v>-18.058406016</v>
+        <v>-25.235317632</v>
       </c>
       <c r="Q53">
-        <v>4.241593984000001</v>
+        <v>-2.935317632</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1658618990856435</v>
+        <v>0.1691426269385769</v>
       </c>
       <c r="T53">
-        <v>1.652697232810944</v>
+        <v>1.697857686588883</v>
       </c>
       <c r="U53">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.08055780292117376</v>
+        <v>0.06728129674391238</v>
       </c>
       <c r="W53">
-        <v>0.1846239931734283</v>
+        <v>0.2199350702277855</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y53">
-        <v>0.503486268257336</v>
+        <v>0.4205081046494524</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1955546974489654</v>
+        <v>0.1974546974489654</v>
       </c>
       <c r="C54">
-        <v>-13.43825223734504</v>
+        <v>-19.80754414281466</v>
       </c>
       <c r="D54">
-        <v>183.1177477626549</v>
+        <v>180.9764558571853</v>
       </c>
       <c r="E54">
-        <v>122.256</v>
+        <v>126.484</v>
       </c>
       <c r="F54">
-        <v>219.856</v>
+        <v>224.084</v>
       </c>
       <c r="G54">
         <v>23.3</v>
@@ -5715,37 +5715,37 @@
         <v>21.8</v>
       </c>
       <c r="M54">
-        <v>51.8420448</v>
+        <v>52.8390072</v>
       </c>
       <c r="N54">
-        <v>-30.0420448</v>
+        <v>-31.0390072</v>
       </c>
       <c r="O54">
-        <v>-4.806727168000001</v>
+        <v>-4.966241151999999</v>
       </c>
       <c r="P54">
-        <v>-25.235317632</v>
+        <v>-26.072766048</v>
       </c>
       <c r="Q54">
-        <v>-2.935317632</v>
+        <v>-3.772766047999998</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1691426269385769</v>
+        <v>0.171766938150036</v>
       </c>
       <c r="T54">
-        <v>1.697857686588883</v>
+        <v>1.733982318218434</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.06728129674391238</v>
+        <v>0.06601183831478197</v>
       </c>
       <c r="W54">
-        <v>0.2199350702277855</v>
+        <v>0.2202344085253744</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.4205081046494524</v>
+        <v>0.4125739894673873</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1974546974489654</v>
+        <v>0.1993546974489654</v>
       </c>
       <c r="C55">
-        <v>-19.80754414281466</v>
+        <v>-26.12733637439368</v>
       </c>
       <c r="D55">
-        <v>180.9764558571853</v>
+        <v>178.8846636256063</v>
       </c>
       <c r="E55">
-        <v>126.484</v>
+        <v>130.712</v>
       </c>
       <c r="F55">
-        <v>224.084</v>
+        <v>228.312</v>
       </c>
       <c r="G55">
         <v>23.3</v>
@@ -5797,37 +5797,37 @@
         <v>21.8</v>
       </c>
       <c r="M55">
-        <v>52.8390072</v>
+        <v>53.8359696</v>
       </c>
       <c r="N55">
-        <v>-31.0390072</v>
+        <v>-32.0359696</v>
       </c>
       <c r="O55">
-        <v>-4.966241151999999</v>
+        <v>-5.125755136</v>
       </c>
       <c r="P55">
-        <v>-26.072766048</v>
+        <v>-26.910214464</v>
       </c>
       <c r="Q55">
-        <v>-3.772766047999998</v>
+        <v>-4.610214463999998</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.171766938150036</v>
+        <v>0.1745053498489498</v>
       </c>
       <c r="T55">
-        <v>1.733982318218434</v>
+        <v>1.771677586005791</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.06601183831478197</v>
+        <v>0.06478939686450823</v>
       </c>
       <c r="W55">
-        <v>0.2202344085253744</v>
+        <v>0.220522660219349</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.4125739894673873</v>
+        <v>0.4049337304031764</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1993546974489654</v>
+        <v>0.2012546974489654</v>
       </c>
       <c r="C56">
-        <v>-26.12733637439368</v>
+        <v>-32.39932572605471</v>
       </c>
       <c r="D56">
-        <v>178.8846636256063</v>
+        <v>176.8406742739453</v>
       </c>
       <c r="E56">
-        <v>130.712</v>
+        <v>134.94</v>
       </c>
       <c r="F56">
-        <v>228.312</v>
+        <v>232.54</v>
       </c>
       <c r="G56">
         <v>23.3</v>
@@ -5879,37 +5879,37 @@
         <v>21.8</v>
       </c>
       <c r="M56">
-        <v>53.8359696</v>
+        <v>54.832932</v>
       </c>
       <c r="N56">
-        <v>-32.0359696</v>
+        <v>-33.032932</v>
       </c>
       <c r="O56">
-        <v>-5.125755136</v>
+        <v>-5.285269120000001</v>
       </c>
       <c r="P56">
-        <v>-26.910214464</v>
+        <v>-27.74766288</v>
       </c>
       <c r="Q56">
-        <v>-4.610214463999998</v>
+        <v>-5.447662879999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1745053498489498</v>
+        <v>0.1773654687344821</v>
       </c>
       <c r="T56">
-        <v>1.771677586005791</v>
+        <v>1.811048199028143</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.06478939686450823</v>
+        <v>0.06361140783060808</v>
       </c>
       <c r="W56">
-        <v>0.220522660219349</v>
+        <v>0.2208004300335426</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.4049337304031764</v>
+        <v>0.3975712989413004</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2012546974489654</v>
+        <v>0.2031546974489654</v>
       </c>
       <c r="C57">
-        <v>-32.39932572605471</v>
+        <v>-38.62513231560527</v>
       </c>
       <c r="D57">
-        <v>176.8406742739453</v>
+        <v>174.8428676843947</v>
       </c>
       <c r="E57">
-        <v>134.94</v>
+        <v>139.168</v>
       </c>
       <c r="F57">
-        <v>232.54</v>
+        <v>236.768</v>
       </c>
       <c r="G57">
         <v>23.3</v>
@@ -5961,37 +5961,37 @@
         <v>21.8</v>
       </c>
       <c r="M57">
-        <v>54.832932</v>
+        <v>55.8298944</v>
       </c>
       <c r="N57">
-        <v>-33.032932</v>
+        <v>-34.0298944</v>
       </c>
       <c r="O57">
-        <v>-5.285269120000001</v>
+        <v>-5.444783104000001</v>
       </c>
       <c r="P57">
-        <v>-27.74766288</v>
+        <v>-28.585111296</v>
       </c>
       <c r="Q57">
-        <v>-5.447662879999999</v>
+        <v>-6.285111296</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1773654687344821</v>
+        <v>0.1803555930239021</v>
       </c>
       <c r="T57">
-        <v>1.811048199028143</v>
+        <v>1.852208385369691</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.06361140783060808</v>
+        <v>0.06247548983363294</v>
       </c>
       <c r="W57">
-        <v>0.2208004300335426</v>
+        <v>0.2210682794972294</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3975712989413004</v>
+        <v>0.3904718114602057</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2031546974489654</v>
+        <v>0.2050546974489654</v>
       </c>
       <c r="C58">
-        <v>-38.62513231560527</v>
+        <v>-44.8063038674394</v>
       </c>
       <c r="D58">
-        <v>174.8428676843947</v>
+        <v>172.8896961325606</v>
       </c>
       <c r="E58">
-        <v>139.168</v>
+        <v>143.396</v>
       </c>
       <c r="F58">
-        <v>236.768</v>
+        <v>240.996</v>
       </c>
       <c r="G58">
         <v>23.3</v>
@@ -6043,37 +6043,37 @@
         <v>21.8</v>
       </c>
       <c r="M58">
-        <v>55.8298944</v>
+        <v>56.8268568</v>
       </c>
       <c r="N58">
-        <v>-34.0298944</v>
+        <v>-35.0268568</v>
       </c>
       <c r="O58">
-        <v>-5.444783104000001</v>
+        <v>-5.604297088000001</v>
       </c>
       <c r="P58">
-        <v>-28.585111296</v>
+        <v>-29.422559712</v>
       </c>
       <c r="Q58">
-        <v>-6.285111296</v>
+        <v>-7.122559712000001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1803555930239021</v>
+        <v>0.1834847928616673</v>
       </c>
       <c r="T58">
-        <v>1.852208385369691</v>
+        <v>1.89528299898294</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.06247548983363294</v>
+        <v>0.06137942860848147</v>
       </c>
       <c r="W58">
-        <v>0.2210682794972294</v>
+        <v>0.2213267307341201</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3904718114602057</v>
+        <v>0.3836214288030092</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2050546974489654</v>
+        <v>0.2069546974489654</v>
       </c>
       <c r="C59">
-        <v>-44.8063038674394</v>
+        <v>-50.94431971140381</v>
       </c>
       <c r="D59">
-        <v>172.8896961325606</v>
+        <v>170.9796802885962</v>
       </c>
       <c r="E59">
-        <v>143.396</v>
+        <v>147.624</v>
       </c>
       <c r="F59">
-        <v>240.996</v>
+        <v>245.224</v>
       </c>
       <c r="G59">
         <v>23.3</v>
@@ -6125,37 +6125,37 @@
         <v>21.8</v>
       </c>
       <c r="M59">
-        <v>56.8268568</v>
+        <v>57.8238192</v>
       </c>
       <c r="N59">
-        <v>-35.0268568</v>
+        <v>-36.02381920000001</v>
       </c>
       <c r="O59">
-        <v>-5.604297088000001</v>
+        <v>-5.763811072000001</v>
       </c>
       <c r="P59">
-        <v>-29.422559712</v>
+        <v>-30.260008128</v>
       </c>
       <c r="Q59">
-        <v>-7.122559712000001</v>
+        <v>-7.960008128000002</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1834847928616673</v>
+        <v>0.1867630022155165</v>
       </c>
       <c r="T59">
-        <v>1.89528299898294</v>
+        <v>1.94040878467301</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.06137942860848147</v>
+        <v>0.06032116259799041</v>
       </c>
       <c r="W59">
-        <v>0.2213267307341201</v>
+        <v>0.2215762698593939</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3836214288030092</v>
+        <v>0.3770072662374401</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2069546974489654</v>
+        <v>0.2088546974489653</v>
       </c>
       <c r="C60">
-        <v>-50.94431971140378</v>
+        <v>-57.04059451949416</v>
       </c>
       <c r="D60">
-        <v>170.9796802885962</v>
+        <v>169.1114054805058</v>
       </c>
       <c r="E60">
-        <v>147.624</v>
+        <v>151.852</v>
       </c>
       <c r="F60">
-        <v>245.224</v>
+        <v>249.452</v>
       </c>
       <c r="G60">
         <v>23.3</v>
@@ -6207,37 +6207,37 @@
         <v>21.8</v>
       </c>
       <c r="M60">
-        <v>57.8238192</v>
+        <v>58.8207816</v>
       </c>
       <c r="N60">
-        <v>-36.02381919999999</v>
+        <v>-37.02078159999999</v>
       </c>
       <c r="O60">
-        <v>-5.763811071999998</v>
+        <v>-5.923325055999999</v>
       </c>
       <c r="P60">
-        <v>-30.26000812799999</v>
+        <v>-31.09745654399999</v>
       </c>
       <c r="Q60">
-        <v>-7.960008127999991</v>
+        <v>-8.797456543999992</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1867630022155165</v>
+        <v>0.190201124220773</v>
       </c>
       <c r="T60">
-        <v>1.940408784673009</v>
+        <v>1.987735828201619</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.06032116259799043</v>
+        <v>0.0592987700115838</v>
       </c>
       <c r="W60">
-        <v>0.2215762698593939</v>
+        <v>0.2218173500312685</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3770072662374402</v>
+        <v>0.3706173125723988</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2088546974489653</v>
+        <v>0.2107546974489653</v>
       </c>
       <c r="C61">
-        <v>-57.04059451949416</v>
+        <v>-63.09648180021583</v>
       </c>
       <c r="D61">
-        <v>169.1114054805058</v>
+        <v>167.2835181997841</v>
       </c>
       <c r="E61">
-        <v>151.852</v>
+        <v>156.08</v>
       </c>
       <c r="F61">
-        <v>249.452</v>
+        <v>253.6799999999999</v>
       </c>
       <c r="G61">
         <v>23.3</v>
@@ -6289,37 +6289,37 @@
         <v>21.8</v>
       </c>
       <c r="M61">
-        <v>58.8207816</v>
+        <v>59.81774399999999</v>
       </c>
       <c r="N61">
-        <v>-37.02078159999999</v>
+        <v>-38.01774399999999</v>
       </c>
       <c r="O61">
-        <v>-5.923325055999999</v>
+        <v>-6.082839039999999</v>
       </c>
       <c r="P61">
-        <v>-31.09745654399999</v>
+        <v>-31.93490495999999</v>
       </c>
       <c r="Q61">
-        <v>-8.797456543999992</v>
+        <v>-9.634904959999993</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.190201124220773</v>
+        <v>0.1938111523262923</v>
       </c>
       <c r="T61">
-        <v>1.987735828201619</v>
+        <v>2.037429223906659</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.0592987700115838</v>
+        <v>0.05831045717805742</v>
       </c>
       <c r="W61">
-        <v>0.2218173500312685</v>
+        <v>0.2220503941974141</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3706173125723988</v>
+        <v>0.3644403573628587</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2107546974489653</v>
+        <v>0.2126546974489653</v>
       </c>
       <c r="C62">
-        <v>-63.09648180021583</v>
+        <v>-69.11327716874982</v>
       </c>
       <c r="D62">
-        <v>167.2835181997841</v>
+        <v>165.4947228312501</v>
       </c>
       <c r="E62">
-        <v>156.08</v>
+        <v>160.308</v>
       </c>
       <c r="F62">
-        <v>253.6799999999999</v>
+        <v>257.908</v>
       </c>
       <c r="G62">
         <v>23.3</v>
@@ -6371,37 +6371,37 @@
         <v>21.8</v>
       </c>
       <c r="M62">
-        <v>59.81774399999999</v>
+        <v>60.81470639999999</v>
       </c>
       <c r="N62">
-        <v>-38.01774399999999</v>
+        <v>-39.01470639999999</v>
       </c>
       <c r="O62">
-        <v>-6.082839039999999</v>
+        <v>-6.242353023999999</v>
       </c>
       <c r="P62">
-        <v>-31.93490495999999</v>
+        <v>-32.772353376</v>
       </c>
       <c r="Q62">
-        <v>-9.634904959999993</v>
+        <v>-10.472353376</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1938111523262923</v>
+        <v>0.1976063100782485</v>
       </c>
       <c r="T62">
-        <v>2.037429223906659</v>
+        <v>2.089670998878626</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.05831045717805742</v>
+        <v>0.05735454804399089</v>
       </c>
       <c r="W62">
-        <v>0.2220503941974141</v>
+        <v>0.222275797571227</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3644403573628587</v>
+        <v>0.358465925274943</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2126546974489653</v>
+        <v>0.2145546974489654</v>
       </c>
       <c r="C63">
-        <v>-69.11327716874982</v>
+        <v>-75.09222140952727</v>
       </c>
       <c r="D63">
-        <v>165.4947228312501</v>
+        <v>163.7437785904727</v>
       </c>
       <c r="E63">
-        <v>160.308</v>
+        <v>164.536</v>
       </c>
       <c r="F63">
-        <v>257.908</v>
+        <v>262.136</v>
       </c>
       <c r="G63">
         <v>23.3</v>
@@ -6453,37 +6453,37 @@
         <v>21.8</v>
       </c>
       <c r="M63">
-        <v>60.81470639999999</v>
+        <v>61.81166879999999</v>
       </c>
       <c r="N63">
-        <v>-39.01470639999999</v>
+        <v>-40.0116688</v>
       </c>
       <c r="O63">
-        <v>-6.242353023999999</v>
+        <v>-6.401867007999999</v>
       </c>
       <c r="P63">
-        <v>-32.772353376</v>
+        <v>-33.609801792</v>
       </c>
       <c r="Q63">
-        <v>-10.472353376</v>
+        <v>-11.309801792</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1976063100782485</v>
+        <v>0.2016012129750445</v>
       </c>
       <c r="T63">
-        <v>2.089670998878626</v>
+        <v>2.144662340954379</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.05735454804399089</v>
+        <v>0.05642947468844265</v>
       </c>
       <c r="W63">
-        <v>0.222275797571227</v>
+        <v>0.2224939298684653</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.358465925274943</v>
+        <v>0.3526842168027665</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2145546974489654</v>
+        <v>0.2164546974489653</v>
       </c>
       <c r="C64">
-        <v>-75.09222140952727</v>
+        <v>-81.03450334642571</v>
       </c>
       <c r="D64">
-        <v>163.7437785904727</v>
+        <v>162.0294966535743</v>
       </c>
       <c r="E64">
-        <v>164.536</v>
+        <v>168.764</v>
       </c>
       <c r="F64">
-        <v>262.136</v>
+        <v>266.364</v>
       </c>
       <c r="G64">
         <v>23.3</v>
@@ -6535,37 +6535,37 @@
         <v>21.8</v>
       </c>
       <c r="M64">
-        <v>61.81166879999999</v>
+        <v>62.80863119999999</v>
       </c>
       <c r="N64">
-        <v>-40.0116688</v>
+        <v>-41.0086312</v>
       </c>
       <c r="O64">
-        <v>-6.401867007999999</v>
+        <v>-6.561380991999999</v>
       </c>
       <c r="P64">
-        <v>-33.609801792</v>
+        <v>-34.447250208</v>
       </c>
       <c r="Q64">
-        <v>-11.309801792</v>
+        <v>-12.147250208</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2016012129750445</v>
+        <v>0.2058120565689646</v>
       </c>
       <c r="T64">
-        <v>2.144662340954379</v>
+        <v>2.2026261880072</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.05642947468844265</v>
+        <v>0.05553376874100706</v>
       </c>
       <c r="W64">
-        <v>0.2224939298684653</v>
+        <v>0.2227051373308706</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3526842168027665</v>
+        <v>0.347086054631294</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2164546974489653</v>
+        <v>0.2183546974489654</v>
       </c>
       <c r="C65">
-        <v>-81.03450334642571</v>
+        <v>-86.94126253454053</v>
       </c>
       <c r="D65">
-        <v>162.0294966535743</v>
+        <v>160.3507374654594</v>
       </c>
       <c r="E65">
-        <v>168.764</v>
+        <v>172.992</v>
       </c>
       <c r="F65">
-        <v>266.364</v>
+        <v>270.592</v>
       </c>
       <c r="G65">
         <v>23.3</v>
@@ -6617,37 +6617,37 @@
         <v>21.8</v>
       </c>
       <c r="M65">
-        <v>62.80863119999999</v>
+        <v>63.8055936</v>
       </c>
       <c r="N65">
-        <v>-41.0086312</v>
+        <v>-42.0055936</v>
       </c>
       <c r="O65">
-        <v>-6.561380991999999</v>
+        <v>-6.720894975999999</v>
       </c>
       <c r="P65">
-        <v>-34.447250208</v>
+        <v>-35.284698624</v>
       </c>
       <c r="Q65">
-        <v>-12.147250208</v>
+        <v>-12.984698624</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2058120565689646</v>
+        <v>0.2102568359181025</v>
       </c>
       <c r="T65">
-        <v>2.2026261880072</v>
+        <v>2.263810248785178</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.05553376874100706</v>
+        <v>0.05466605360442881</v>
       </c>
       <c r="W65">
-        <v>0.2227051373308706</v>
+        <v>0.2229097445600757</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.347086054631294</v>
+        <v>0.3416628350276801</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2183546974489654</v>
+        <v>0.2202546974489654</v>
       </c>
       <c r="C66">
-        <v>-86.94126253454053</v>
+        <v>-92.81359178633735</v>
       </c>
       <c r="D66">
-        <v>160.3507374654594</v>
+        <v>158.7064082136626</v>
       </c>
       <c r="E66">
-        <v>172.992</v>
+        <v>177.22</v>
       </c>
       <c r="F66">
-        <v>270.592</v>
+        <v>274.82</v>
       </c>
       <c r="G66">
         <v>23.3</v>
@@ -6699,37 +6699,37 @@
         <v>21.8</v>
       </c>
       <c r="M66">
-        <v>63.8055936</v>
+        <v>64.802556</v>
       </c>
       <c r="N66">
-        <v>-42.0055936</v>
+        <v>-43.002556</v>
       </c>
       <c r="O66">
-        <v>-6.720894975999999</v>
+        <v>-6.88040896</v>
       </c>
       <c r="P66">
-        <v>-35.284698624</v>
+        <v>-36.12214704</v>
       </c>
       <c r="Q66">
-        <v>-12.984698624</v>
+        <v>-13.82214704</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2102568359181025</v>
+        <v>0.2149556026586198</v>
       </c>
       <c r="T66">
-        <v>2.263810248785178</v>
+        <v>2.328490541607612</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.05466605360442881</v>
+        <v>0.05382503739512991</v>
       </c>
       <c r="W66">
-        <v>0.2229097445600757</v>
+        <v>0.2231080561822284</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3416628350276801</v>
+        <v>0.3364064837195619</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2202546974489654</v>
+        <v>0.2221546974489654</v>
       </c>
       <c r="C67">
-        <v>-92.81359178633735</v>
+        <v>-98.65253954395527</v>
       </c>
       <c r="D67">
-        <v>158.7064082136626</v>
+        <v>157.0954604560447</v>
       </c>
       <c r="E67">
-        <v>177.22</v>
+        <v>181.448</v>
       </c>
       <c r="F67">
-        <v>274.82</v>
+        <v>279.048</v>
       </c>
       <c r="G67">
         <v>23.3</v>
@@ -6781,37 +6781,37 @@
         <v>21.8</v>
       </c>
       <c r="M67">
-        <v>64.802556</v>
+        <v>65.7995184</v>
       </c>
       <c r="N67">
-        <v>-43.002556</v>
+        <v>-43.9995184</v>
       </c>
       <c r="O67">
-        <v>-6.88040896</v>
+        <v>-7.039922944</v>
       </c>
       <c r="P67">
-        <v>-36.12214704</v>
+        <v>-36.959595456</v>
       </c>
       <c r="Q67">
-        <v>-13.82214704</v>
+        <v>-14.659595456</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2149556026586198</v>
+        <v>0.2199307674426969</v>
       </c>
       <c r="T67">
-        <v>2.328490541607612</v>
+        <v>2.396975557537247</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.05382503739512991</v>
+        <v>0.05300950652550673</v>
       </c>
       <c r="W67">
-        <v>0.2231080561822284</v>
+        <v>0.2233003583612855</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3364064837195619</v>
+        <v>0.331309415784417</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2221546974489654</v>
+        <v>0.2240546974489654</v>
       </c>
       <c r="C68">
-        <v>-98.65253954395527</v>
+        <v>-104.4591121084813</v>
       </c>
       <c r="D68">
-        <v>157.0954604560447</v>
+        <v>155.5168878915187</v>
       </c>
       <c r="E68">
-        <v>181.448</v>
+        <v>185.676</v>
       </c>
       <c r="F68">
-        <v>279.048</v>
+        <v>283.276</v>
       </c>
       <c r="G68">
         <v>23.3</v>
@@ -6863,37 +6863,37 @@
         <v>21.8</v>
       </c>
       <c r="M68">
-        <v>65.7995184</v>
+        <v>66.79648080000001</v>
       </c>
       <c r="N68">
-        <v>-43.9995184</v>
+        <v>-44.99648080000001</v>
       </c>
       <c r="O68">
-        <v>-7.039922944</v>
+        <v>-7.199436928000003</v>
       </c>
       <c r="P68">
-        <v>-36.959595456</v>
+        <v>-37.79704387200001</v>
       </c>
       <c r="Q68">
-        <v>-14.659595456</v>
+        <v>-15.49704387200001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2199307674426969</v>
+        <v>0.2252074573652028</v>
       </c>
       <c r="T68">
-        <v>2.396975557537247</v>
+        <v>2.469611180492921</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.05300950652550673</v>
+        <v>0.05221831986094692</v>
       </c>
       <c r="W68">
-        <v>0.2233003583612855</v>
+        <v>0.2234869201767887</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.331309415784417</v>
+        <v>0.3263644991309181</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2240546974489654</v>
+        <v>0.2259546974489654</v>
       </c>
       <c r="C69">
-        <v>-104.4591121084813</v>
+        <v>-110.2342757361569</v>
       </c>
       <c r="D69">
-        <v>155.5168878915187</v>
+        <v>153.969724263843</v>
       </c>
       <c r="E69">
-        <v>185.676</v>
+        <v>189.904</v>
       </c>
       <c r="F69">
-        <v>283.276</v>
+        <v>287.504</v>
       </c>
       <c r="G69">
         <v>23.3</v>
@@ -6945,37 +6945,37 @@
         <v>21.8</v>
       </c>
       <c r="M69">
-        <v>66.79648080000001</v>
+        <v>67.7934432</v>
       </c>
       <c r="N69">
-        <v>-44.99648080000001</v>
+        <v>-45.9934432</v>
       </c>
       <c r="O69">
-        <v>-7.199436928000003</v>
+        <v>-7.358950912</v>
       </c>
       <c r="P69">
-        <v>-37.79704387200001</v>
+        <v>-38.634492288</v>
       </c>
       <c r="Q69">
-        <v>-15.49704387200001</v>
+        <v>-16.334492288</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2252074573652028</v>
+        <v>0.2308139404078654</v>
       </c>
       <c r="T69">
-        <v>2.469611180492921</v>
+        <v>2.546786529883325</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.05221831986094692</v>
+        <v>0.05145040339240359</v>
       </c>
       <c r="W69">
-        <v>0.2234869201767887</v>
+        <v>0.2236679948800712</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3263644991309181</v>
+        <v>0.3215650212025224</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2259546974489654</v>
+        <v>0.2278546974489654</v>
       </c>
       <c r="C70">
-        <v>-110.2342757361569</v>
+        <v>-115.978958610692</v>
       </c>
       <c r="D70">
-        <v>153.969724263843</v>
+        <v>152.4530413893079</v>
       </c>
       <c r="E70">
-        <v>189.904</v>
+        <v>194.132</v>
       </c>
       <c r="F70">
-        <v>287.504</v>
+        <v>291.732</v>
       </c>
       <c r="G70">
         <v>23.3</v>
@@ -7027,37 +7027,37 @@
         <v>21.8</v>
       </c>
       <c r="M70">
-        <v>67.7934432</v>
+        <v>68.7904056</v>
       </c>
       <c r="N70">
-        <v>-45.9934432</v>
+        <v>-46.9904056</v>
       </c>
       <c r="O70">
-        <v>-7.358950912</v>
+        <v>-7.518464896</v>
       </c>
       <c r="P70">
-        <v>-38.634492288</v>
+        <v>-39.471940704</v>
       </c>
       <c r="Q70">
-        <v>-16.334492288</v>
+        <v>-17.171940704</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2308139404078654</v>
+        <v>0.2367821320339256</v>
       </c>
       <c r="T70">
-        <v>2.546786529883325</v>
+        <v>2.62894093407311</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.05145040339240359</v>
+        <v>0.05070474537222383</v>
       </c>
       <c r="W70">
-        <v>0.2236679948800712</v>
+        <v>0.2238438210412296</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3215650212025224</v>
+        <v>0.3169046585763988</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2278546974489654</v>
+        <v>0.2297546974489653</v>
       </c>
       <c r="C71">
-        <v>-115.978958610692</v>
+        <v>-121.6940527001462</v>
       </c>
       <c r="D71">
-        <v>152.4530413893079</v>
+        <v>150.9659472998538</v>
       </c>
       <c r="E71">
-        <v>194.132</v>
+        <v>198.36</v>
       </c>
       <c r="F71">
-        <v>291.732</v>
+        <v>295.96</v>
       </c>
       <c r="G71">
         <v>23.3</v>
@@ -7109,37 +7109,37 @@
         <v>21.8</v>
       </c>
       <c r="M71">
-        <v>68.7904056</v>
+        <v>69.787368</v>
       </c>
       <c r="N71">
-        <v>-46.9904056</v>
+        <v>-47.987368</v>
       </c>
       <c r="O71">
-        <v>-7.518464896</v>
+        <v>-7.67797888</v>
       </c>
       <c r="P71">
-        <v>-39.471940704</v>
+        <v>-40.30938912000001</v>
       </c>
       <c r="Q71">
-        <v>-17.171940704</v>
+        <v>-18.00938912000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2367821320339256</v>
+        <v>0.2431482031017231</v>
       </c>
       <c r="T71">
-        <v>2.62894093407311</v>
+        <v>2.716572298542213</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.05070474537222383</v>
+        <v>0.04998039186690635</v>
       </c>
       <c r="W71">
-        <v>0.2238438210412296</v>
+        <v>0.2240146235977835</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3169046585763988</v>
+        <v>0.3123774491681646</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2297546974489653</v>
+        <v>0.2316546974489654</v>
       </c>
       <c r="C72">
-        <v>-121.6940527001462</v>
+        <v>-127.3804155061829</v>
       </c>
       <c r="D72">
-        <v>150.9659472998538</v>
+        <v>149.5075844938171</v>
       </c>
       <c r="E72">
-        <v>198.36</v>
+        <v>202.588</v>
       </c>
       <c r="F72">
-        <v>295.96</v>
+        <v>300.188</v>
       </c>
       <c r="G72">
         <v>23.3</v>
@@ -7191,37 +7191,37 @@
         <v>21.8</v>
       </c>
       <c r="M72">
-        <v>69.787368</v>
+        <v>70.7843304</v>
       </c>
       <c r="N72">
-        <v>-47.987368</v>
+        <v>-48.9843304</v>
       </c>
       <c r="O72">
-        <v>-7.67797888</v>
+        <v>-7.837492864000001</v>
       </c>
       <c r="P72">
-        <v>-40.30938912000001</v>
+        <v>-41.14683753600001</v>
       </c>
       <c r="Q72">
-        <v>-18.00938912000001</v>
+        <v>-18.84683753600001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2431482031017231</v>
+        <v>0.2499533135535067</v>
       </c>
       <c r="T72">
-        <v>2.716572298542213</v>
+        <v>2.810247205388497</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.04998039186690635</v>
+        <v>0.04927644268568231</v>
       </c>
       <c r="W72">
-        <v>0.2240146235977835</v>
+        <v>0.2241806148147161</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3123774491681646</v>
+        <v>0.3079777667855144</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2316546974489654</v>
+        <v>0.2335546974489653</v>
       </c>
       <c r="C73">
-        <v>-127.3804155061828</v>
+        <v>-133.038871712904</v>
       </c>
       <c r="D73">
-        <v>149.5075844938171</v>
+        <v>148.0771282870959</v>
       </c>
       <c r="E73">
-        <v>202.5879999999999</v>
+        <v>206.8159999999999</v>
       </c>
       <c r="F73">
-        <v>300.1879999999999</v>
+        <v>304.4159999999999</v>
       </c>
       <c r="G73">
         <v>23.3</v>
@@ -7273,37 +7273,37 @@
         <v>21.8</v>
       </c>
       <c r="M73">
-        <v>70.78433039999999</v>
+        <v>71.78129279999999</v>
       </c>
       <c r="N73">
-        <v>-48.98433039999999</v>
+        <v>-49.98129279999999</v>
       </c>
       <c r="O73">
-        <v>-7.837492863999999</v>
+        <v>-7.997006847999999</v>
       </c>
       <c r="P73">
-        <v>-41.14683753599999</v>
+        <v>-41.98428595199999</v>
       </c>
       <c r="Q73">
-        <v>-18.84683753599999</v>
+        <v>-19.68428595199999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2499533135535066</v>
+        <v>0.2572445033232746</v>
       </c>
       <c r="T73">
-        <v>2.810247205388496</v>
+        <v>2.910613177009513</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.04927644268568233</v>
+        <v>0.04859204764838117</v>
       </c>
       <c r="W73">
-        <v>0.2241806148147161</v>
+        <v>0.2243419951645117</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3079777667855145</v>
+        <v>0.3037002978023823</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2335546974489653</v>
+        <v>0.2354546974489654</v>
       </c>
       <c r="C74">
-        <v>-133.038871712904</v>
+        <v>-138.6702147419286</v>
       </c>
       <c r="D74">
-        <v>148.0771282870959</v>
+        <v>146.6737852580713</v>
       </c>
       <c r="E74">
-        <v>206.8159999999999</v>
+        <v>211.044</v>
       </c>
       <c r="F74">
-        <v>304.4159999999999</v>
+        <v>308.6439999999999</v>
       </c>
       <c r="G74">
         <v>23.3</v>
@@ -7355,37 +7355,37 @@
         <v>21.8</v>
       </c>
       <c r="M74">
-        <v>71.78129279999999</v>
+        <v>72.77825519999999</v>
       </c>
       <c r="N74">
-        <v>-49.98129279999999</v>
+        <v>-50.97825519999999</v>
       </c>
       <c r="O74">
-        <v>-7.997006847999999</v>
+        <v>-8.156520831999998</v>
       </c>
       <c r="P74">
-        <v>-41.98428595199999</v>
+        <v>-42.82173436799999</v>
       </c>
       <c r="Q74">
-        <v>-19.68428595199999</v>
+        <v>-20.52173436799999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2572445033232746</v>
+        <v>0.2650757812241367</v>
       </c>
       <c r="T74">
-        <v>2.910613177009513</v>
+        <v>3.018413665046903</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.04859204764838117</v>
+        <v>0.04792640316004719</v>
       </c>
       <c r="W74">
-        <v>0.2243419951645117</v>
+        <v>0.2244989541348609</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3037002978023823</v>
+        <v>0.2995400197502949</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2354546974489654</v>
+        <v>0.2373546974489654</v>
       </c>
       <c r="C75">
-        <v>-138.6702147419286</v>
+        <v>-144.2752082198744</v>
       </c>
       <c r="D75">
-        <v>146.6737852580713</v>
+        <v>145.2967917801256</v>
       </c>
       <c r="E75">
-        <v>211.044</v>
+        <v>215.272</v>
       </c>
       <c r="F75">
-        <v>308.6439999999999</v>
+        <v>312.872</v>
       </c>
       <c r="G75">
         <v>23.3</v>
@@ -7437,37 +7437,37 @@
         <v>21.8</v>
       </c>
       <c r="M75">
-        <v>72.77825519999999</v>
+        <v>73.77521759999999</v>
       </c>
       <c r="N75">
-        <v>-50.97825519999999</v>
+        <v>-51.97521759999999</v>
       </c>
       <c r="O75">
-        <v>-8.156520831999998</v>
+        <v>-8.316034815999998</v>
       </c>
       <c r="P75">
-        <v>-42.82173436799999</v>
+        <v>-43.659182784</v>
       </c>
       <c r="Q75">
-        <v>-20.52173436799999</v>
+        <v>-21.35918278399999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2650757812241367</v>
+        <v>0.2735094651173727</v>
       </c>
       <c r="T75">
-        <v>3.018413665046903</v>
+        <v>3.134506498317938</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.04792640316004719</v>
+        <v>0.04727874906328979</v>
       </c>
       <c r="W75">
-        <v>0.2244989541348609</v>
+        <v>0.2246516709708763</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2995400197502949</v>
+        <v>0.2954921816455611</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2373546974489654</v>
+        <v>0.2392546974489654</v>
       </c>
       <c r="C76">
-        <v>-144.2752082198744</v>
+        <v>-149.8545873639478</v>
       </c>
       <c r="D76">
-        <v>145.2967917801256</v>
+        <v>143.9454126360522</v>
       </c>
       <c r="E76">
-        <v>215.272</v>
+        <v>219.5</v>
       </c>
       <c r="F76">
-        <v>312.872</v>
+        <v>317.1</v>
       </c>
       <c r="G76">
         <v>23.3</v>
@@ -7519,37 +7519,37 @@
         <v>21.8</v>
       </c>
       <c r="M76">
-        <v>73.77521759999999</v>
+        <v>74.77217999999999</v>
       </c>
       <c r="N76">
-        <v>-51.97521759999999</v>
+        <v>-52.97217999999999</v>
       </c>
       <c r="O76">
-        <v>-8.316034815999998</v>
+        <v>-8.475548799999999</v>
       </c>
       <c r="P76">
-        <v>-43.659182784</v>
+        <v>-44.4966312</v>
       </c>
       <c r="Q76">
-        <v>-21.35918278399999</v>
+        <v>-22.1966312</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2735094651173727</v>
+        <v>0.2826178437220677</v>
       </c>
       <c r="T76">
-        <v>3.134506498317938</v>
+        <v>3.259886758250656</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.04727874906328979</v>
+        <v>0.04664836574244593</v>
       </c>
       <c r="W76">
-        <v>0.2246516709708763</v>
+        <v>0.2248003153579313</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2954921816455611</v>
+        <v>0.291552285890287</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2392546974489654</v>
+        <v>0.2411546974489653</v>
       </c>
       <c r="C77">
-        <v>-149.8545873639478</v>
+        <v>-155.409060290923</v>
       </c>
       <c r="D77">
-        <v>143.9454126360522</v>
+        <v>142.6189397090769</v>
       </c>
       <c r="E77">
-        <v>219.5</v>
+        <v>223.728</v>
       </c>
       <c r="F77">
-        <v>317.1</v>
+        <v>321.328</v>
       </c>
       <c r="G77">
         <v>23.3</v>
@@ -7601,37 +7601,37 @@
         <v>21.8</v>
       </c>
       <c r="M77">
-        <v>74.77217999999999</v>
+        <v>75.76914239999999</v>
       </c>
       <c r="N77">
-        <v>-52.97217999999999</v>
+        <v>-53.9691424</v>
       </c>
       <c r="O77">
-        <v>-8.475548799999999</v>
+        <v>-8.635062783999999</v>
       </c>
       <c r="P77">
-        <v>-44.4966312</v>
+        <v>-45.334079616</v>
       </c>
       <c r="Q77">
-        <v>-22.1966312</v>
+        <v>-23.034079616</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2826178437220677</v>
+        <v>0.2924852538771538</v>
       </c>
       <c r="T77">
-        <v>3.259886758250656</v>
+        <v>3.395715373177767</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.04664836574244593</v>
+        <v>0.04603457145636111</v>
       </c>
       <c r="W77">
-        <v>0.2248003153579313</v>
+        <v>0.22494504805059</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.291552285890287</v>
+        <v>0.2877160716022569</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2411546974489653</v>
+        <v>0.2430546974489654</v>
       </c>
       <c r="C78">
-        <v>-155.409060290923</v>
+        <v>-160.9393092544084</v>
       </c>
       <c r="D78">
-        <v>142.6189397090769</v>
+        <v>141.3166907455916</v>
       </c>
       <c r="E78">
-        <v>223.728</v>
+        <v>227.956</v>
       </c>
       <c r="F78">
-        <v>321.328</v>
+        <v>325.556</v>
       </c>
       <c r="G78">
         <v>23.3</v>
@@ -7683,37 +7683,37 @@
         <v>21.8</v>
       </c>
       <c r="M78">
-        <v>75.76914239999999</v>
+        <v>76.76610479999999</v>
       </c>
       <c r="N78">
-        <v>-53.9691424</v>
+        <v>-54.9661048</v>
       </c>
       <c r="O78">
-        <v>-8.635062783999999</v>
+        <v>-8.794576767999999</v>
       </c>
       <c r="P78">
-        <v>-45.334079616</v>
+        <v>-46.171528032</v>
       </c>
       <c r="Q78">
-        <v>-23.034079616</v>
+        <v>-23.871528032</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2924852538771538</v>
+        <v>0.3032106996978997</v>
       </c>
       <c r="T78">
-        <v>3.395715373177767</v>
+        <v>3.543355172011582</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.04603457145636111</v>
+        <v>0.04543671987900577</v>
       </c>
       <c r="W78">
-        <v>0.22494504805059</v>
+        <v>0.2250860214525305</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2877160716022569</v>
+        <v>0.2839794992437861</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2430546974489654</v>
+        <v>0.2449546974489653</v>
       </c>
       <c r="C79">
-        <v>-160.9393092544084</v>
+        <v>-166.4459918149403</v>
       </c>
       <c r="D79">
-        <v>141.3166907455916</v>
+        <v>140.0380081850597</v>
       </c>
       <c r="E79">
-        <v>227.956</v>
+        <v>232.184</v>
       </c>
       <c r="F79">
-        <v>325.556</v>
+        <v>329.784</v>
       </c>
       <c r="G79">
         <v>23.3</v>
@@ -7765,37 +7765,37 @@
         <v>21.8</v>
       </c>
       <c r="M79">
-        <v>76.76610479999999</v>
+        <v>77.76306719999999</v>
       </c>
       <c r="N79">
-        <v>-54.9661048</v>
+        <v>-55.9630672</v>
       </c>
       <c r="O79">
-        <v>-8.794576767999999</v>
+        <v>-8.954090751999999</v>
       </c>
       <c r="P79">
-        <v>-46.171528032</v>
+        <v>-47.008976448</v>
       </c>
       <c r="Q79">
-        <v>-23.871528032</v>
+        <v>-24.708976448</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3032106996978997</v>
+        <v>0.3149111860478042</v>
       </c>
       <c r="T79">
-        <v>3.543355172011582</v>
+        <v>3.704416770739381</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.04543671987900577</v>
+        <v>0.04485419782927493</v>
       </c>
       <c r="W79">
-        <v>0.2250860214525305</v>
+        <v>0.225223380151857</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2839794992437861</v>
+        <v>0.2803387364329682</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2449546974489653</v>
+        <v>0.2468546974489653</v>
       </c>
       <c r="C80">
-        <v>-166.4459918149403</v>
+        <v>-171.9297419471234</v>
       </c>
       <c r="D80">
-        <v>140.0380081850597</v>
+        <v>138.7822580528766</v>
       </c>
       <c r="E80">
-        <v>232.184</v>
+        <v>236.412</v>
       </c>
       <c r="F80">
-        <v>329.784</v>
+        <v>334.012</v>
       </c>
       <c r="G80">
         <v>23.3</v>
@@ -7847,37 +7847,37 @@
         <v>21.8</v>
       </c>
       <c r="M80">
-        <v>77.76306719999999</v>
+        <v>78.76002960000001</v>
       </c>
       <c r="N80">
-        <v>-55.9630672</v>
+        <v>-56.96002960000001</v>
       </c>
       <c r="O80">
-        <v>-8.954090751999999</v>
+        <v>-9.113604736000003</v>
       </c>
       <c r="P80">
-        <v>-47.008976448</v>
+        <v>-47.84642486400001</v>
       </c>
       <c r="Q80">
-        <v>-24.708976448</v>
+        <v>-25.54642486400001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3149111860478042</v>
+        <v>0.3277260044310329</v>
       </c>
       <c r="T80">
-        <v>3.704416770739381</v>
+        <v>3.880817569346019</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.04485419782927493</v>
+        <v>0.04428642317320815</v>
       </c>
       <c r="W80">
-        <v>0.225223380151857</v>
+        <v>0.2253572614157575</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2803387364329682</v>
+        <v>0.2767901448325509</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2468546974489653</v>
+        <v>0.2487546974489653</v>
       </c>
       <c r="C81">
-        <v>-171.9297419471234</v>
+        <v>-177.3911710877318</v>
       </c>
       <c r="D81">
-        <v>138.7822580528766</v>
+        <v>137.5488289122682</v>
       </c>
       <c r="E81">
-        <v>236.412</v>
+        <v>240.64</v>
       </c>
       <c r="F81">
-        <v>334.012</v>
+        <v>338.24</v>
       </c>
       <c r="G81">
         <v>23.3</v>
@@ -7929,37 +7929,37 @@
         <v>21.8</v>
       </c>
       <c r="M81">
-        <v>78.76002960000001</v>
+        <v>79.75699200000001</v>
       </c>
       <c r="N81">
-        <v>-56.96002960000001</v>
+        <v>-57.95699200000001</v>
       </c>
       <c r="O81">
-        <v>-9.113604736000003</v>
+        <v>-9.273118720000003</v>
       </c>
       <c r="P81">
-        <v>-47.84642486400001</v>
+        <v>-48.68387328000001</v>
       </c>
       <c r="Q81">
-        <v>-25.54642486400001</v>
+        <v>-26.38387328000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3277260044310329</v>
+        <v>0.3418223046525846</v>
       </c>
       <c r="T81">
-        <v>3.880817569346019</v>
+        <v>4.074858447813321</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.04428642317320815</v>
+        <v>0.04373284288354305</v>
       </c>
       <c r="W81">
-        <v>0.2253572614157575</v>
+        <v>0.2254877956480605</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2767901448325509</v>
+        <v>0.273330268022144</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2487546974489653</v>
+        <v>0.2506546974489653</v>
       </c>
       <c r="C82">
-        <v>-177.3911710877318</v>
+        <v>-182.8308691284128</v>
       </c>
       <c r="D82">
-        <v>137.5488289122682</v>
+        <v>136.3371308715872</v>
       </c>
       <c r="E82">
-        <v>240.64</v>
+        <v>244.868</v>
       </c>
       <c r="F82">
-        <v>338.24</v>
+        <v>342.468</v>
       </c>
       <c r="G82">
         <v>23.3</v>
@@ -8011,37 +8011,37 @@
         <v>21.8</v>
       </c>
       <c r="M82">
-        <v>79.75699200000001</v>
+        <v>80.7539544</v>
       </c>
       <c r="N82">
-        <v>-57.95699200000001</v>
+        <v>-58.9539544</v>
       </c>
       <c r="O82">
-        <v>-9.273118720000003</v>
+        <v>-9.432632704</v>
       </c>
       <c r="P82">
-        <v>-48.68387328000001</v>
+        <v>-49.521321696</v>
       </c>
       <c r="Q82">
-        <v>-26.38387328000001</v>
+        <v>-27.221321696</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3418223046525846</v>
+        <v>0.3574024259500891</v>
       </c>
       <c r="T82">
-        <v>4.074858447813321</v>
+        <v>4.289324681908758</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.04373284288354305</v>
+        <v>0.04319293124300549</v>
       </c>
       <c r="W82">
-        <v>0.2254877956480605</v>
+        <v>0.2256151068128993</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.273330268022144</v>
+        <v>0.2699558202687843</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2506546974489653</v>
+        <v>0.2525546974489654</v>
       </c>
       <c r="C83">
-        <v>-182.8308691284128</v>
+        <v>-188.249405356379</v>
       </c>
       <c r="D83">
-        <v>136.3371308715872</v>
+        <v>135.146594643621</v>
       </c>
       <c r="E83">
-        <v>244.868</v>
+        <v>249.096</v>
       </c>
       <c r="F83">
-        <v>342.468</v>
+        <v>346.696</v>
       </c>
       <c r="G83">
         <v>23.3</v>
@@ -8093,37 +8093,37 @@
         <v>21.8</v>
       </c>
       <c r="M83">
-        <v>80.7539544</v>
+        <v>81.7509168</v>
       </c>
       <c r="N83">
-        <v>-58.9539544</v>
+        <v>-59.9509168</v>
       </c>
       <c r="O83">
-        <v>-9.432632704</v>
+        <v>-9.592146688</v>
       </c>
       <c r="P83">
-        <v>-49.521321696</v>
+        <v>-50.358770112</v>
       </c>
       <c r="Q83">
-        <v>-27.221321696</v>
+        <v>-28.058770112</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3574024259500891</v>
+        <v>0.3747136718362052</v>
       </c>
       <c r="T83">
-        <v>4.289324681908758</v>
+        <v>4.527620497570356</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.04319293124300549</v>
+        <v>0.04266618817906639</v>
       </c>
       <c r="W83">
-        <v>0.2256151068128993</v>
+        <v>0.2257393128273761</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2699558202687843</v>
+        <v>0.2666636761191649</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2525546974489654</v>
+        <v>0.2544546974489654</v>
       </c>
       <c r="C84">
-        <v>-188.249405356379</v>
+        <v>-193.6473293462408</v>
       </c>
       <c r="D84">
-        <v>135.146594643621</v>
+        <v>133.9766706537591</v>
       </c>
       <c r="E84">
-        <v>249.096</v>
+        <v>253.324</v>
       </c>
       <c r="F84">
-        <v>346.696</v>
+        <v>350.924</v>
       </c>
       <c r="G84">
         <v>23.3</v>
@@ -8175,37 +8175,37 @@
         <v>21.8</v>
       </c>
       <c r="M84">
-        <v>81.7509168</v>
+        <v>82.7478792</v>
       </c>
       <c r="N84">
-        <v>-59.9509168</v>
+        <v>-60.9478792</v>
       </c>
       <c r="O84">
-        <v>-9.592146688</v>
+        <v>-9.751660672</v>
       </c>
       <c r="P84">
-        <v>-50.358770112</v>
+        <v>-51.196218528</v>
       </c>
       <c r="Q84">
-        <v>-28.058770112</v>
+        <v>-28.896218528</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3747136718362052</v>
+        <v>0.3940615348853937</v>
       </c>
       <c r="T84">
-        <v>4.527620497570356</v>
+        <v>4.793951115074495</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.04266618817906639</v>
+        <v>0.04215213771907764</v>
       </c>
       <c r="W84">
-        <v>0.2257393128273761</v>
+        <v>0.2258605259258415</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2666636761191649</v>
+        <v>0.2634508607442352</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2544546974489654</v>
+        <v>0.2563546974489654</v>
       </c>
       <c r="C85">
-        <v>-193.6473293462408</v>
+        <v>-199.0251718059143</v>
       </c>
       <c r="D85">
-        <v>133.9766706537591</v>
+        <v>132.8268281940856</v>
       </c>
       <c r="E85">
-        <v>253.324</v>
+        <v>257.552</v>
       </c>
       <c r="F85">
-        <v>350.924</v>
+        <v>355.152</v>
       </c>
       <c r="G85">
         <v>23.3</v>
@@ -8257,37 +8257,37 @@
         <v>21.8</v>
       </c>
       <c r="M85">
-        <v>82.7478792</v>
+        <v>83.7448416</v>
       </c>
       <c r="N85">
-        <v>-60.9478792</v>
+        <v>-61.9448416</v>
       </c>
       <c r="O85">
-        <v>-9.751660672</v>
+        <v>-9.911174656</v>
       </c>
       <c r="P85">
-        <v>-51.196218528</v>
+        <v>-52.033666944</v>
       </c>
       <c r="Q85">
-        <v>-28.896218528</v>
+        <v>-29.733666944</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3940615348853937</v>
+        <v>0.4158278808157309</v>
       </c>
       <c r="T85">
-        <v>4.793951115074495</v>
+        <v>5.093573059766652</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.04215213771907764</v>
+        <v>0.04165032655575529</v>
       </c>
       <c r="W85">
-        <v>0.2258605259258415</v>
+        <v>0.2259788529981529</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2634508607442352</v>
+        <v>0.2603145409734705</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2563546974489653</v>
+        <v>0.2582546974489653</v>
       </c>
       <c r="C86">
-        <v>-199.0251718059142</v>
+        <v>-204.3834453793402</v>
       </c>
       <c r="D86">
-        <v>132.8268281940857</v>
+        <v>131.6965546206597</v>
       </c>
       <c r="E86">
-        <v>257.5519999999999</v>
+        <v>261.78</v>
       </c>
       <c r="F86">
-        <v>355.1519999999999</v>
+        <v>359.3799999999999</v>
       </c>
       <c r="G86">
         <v>23.3</v>
@@ -8339,37 +8339,37 @@
         <v>21.8</v>
       </c>
       <c r="M86">
-        <v>83.74484159999999</v>
+        <v>84.74180399999999</v>
       </c>
       <c r="N86">
-        <v>-61.94484159999999</v>
+        <v>-62.94180399999999</v>
       </c>
       <c r="O86">
-        <v>-9.911174655999998</v>
+        <v>-10.07068864</v>
       </c>
       <c r="P86">
-        <v>-52.03366694399999</v>
+        <v>-52.87111535999999</v>
       </c>
       <c r="Q86">
-        <v>-29.73366694399999</v>
+        <v>-30.57111535999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4158278808157306</v>
+        <v>0.440496406203446</v>
       </c>
       <c r="T86">
-        <v>5.093573059766649</v>
+        <v>5.433144597084425</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.04165032655575529</v>
+        <v>0.04116032271392288</v>
       </c>
       <c r="W86">
-        <v>0.2259788529981529</v>
+        <v>0.226094395904057</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2603145409734705</v>
+        <v>0.2572520169620179</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2582546974489653</v>
+        <v>0.2601546974489654</v>
       </c>
       <c r="C87">
-        <v>-204.3834453793402</v>
+        <v>-209.7226454085655</v>
       </c>
       <c r="D87">
-        <v>131.6965546206597</v>
+        <v>130.5853545914344</v>
       </c>
       <c r="E87">
-        <v>261.78</v>
+        <v>266.0079999999999</v>
       </c>
       <c r="F87">
-        <v>359.3799999999999</v>
+        <v>363.6079999999999</v>
       </c>
       <c r="G87">
         <v>23.3</v>
@@ -8421,37 +8421,37 @@
         <v>21.8</v>
       </c>
       <c r="M87">
-        <v>84.74180399999999</v>
+        <v>85.73876639999999</v>
       </c>
       <c r="N87">
-        <v>-62.94180399999999</v>
+        <v>-63.93876639999999</v>
       </c>
       <c r="O87">
-        <v>-10.07068864</v>
+        <v>-10.230202624</v>
       </c>
       <c r="P87">
-        <v>-52.87111535999999</v>
+        <v>-53.70856377599999</v>
       </c>
       <c r="Q87">
-        <v>-30.57111535999999</v>
+        <v>-31.40856377599999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.440496406203446</v>
+        <v>0.4686890066465494</v>
       </c>
       <c r="T87">
-        <v>5.433144597084425</v>
+        <v>5.821226354019028</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.04116032271392288</v>
+        <v>0.04068171431027261</v>
       </c>
       <c r="W87">
-        <v>0.226094395904057</v>
+        <v>0.2262072517656377</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2572520169620179</v>
+        <v>0.2542607144392037</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2601546974489654</v>
+        <v>0.2620546974489654</v>
       </c>
       <c r="C88">
-        <v>-209.7226454085655</v>
+        <v>-215.0432506575656</v>
       </c>
       <c r="D88">
-        <v>130.5853545914344</v>
+        <v>129.4927493424343</v>
       </c>
       <c r="E88">
-        <v>266.0079999999999</v>
+        <v>270.236</v>
       </c>
       <c r="F88">
-        <v>363.6079999999999</v>
+        <v>367.836</v>
       </c>
       <c r="G88">
         <v>23.3</v>
@@ -8503,37 +8503,37 @@
         <v>21.8</v>
       </c>
       <c r="M88">
-        <v>85.73876639999999</v>
+        <v>86.73572879999999</v>
       </c>
       <c r="N88">
-        <v>-63.93876639999999</v>
+        <v>-64.93572879999999</v>
       </c>
       <c r="O88">
-        <v>-10.230202624</v>
+        <v>-10.389716608</v>
       </c>
       <c r="P88">
-        <v>-53.70856377599999</v>
+        <v>-54.54601219199999</v>
       </c>
       <c r="Q88">
-        <v>-31.40856377599999</v>
+        <v>-32.24601219199999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4686890066465494</v>
+        <v>0.5012189302347454</v>
       </c>
       <c r="T88">
-        <v>5.821226354019028</v>
+        <v>6.269012996635876</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.04068171431027261</v>
+        <v>0.04021410839866029</v>
       </c>
       <c r="W88">
-        <v>0.2262072517656377</v>
+        <v>0.2263175132395959</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2542607144392037</v>
+        <v>0.2513381774916267</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2620546974489654</v>
+        <v>0.2639546974489654</v>
       </c>
       <c r="C89">
-        <v>-215.0432506575656</v>
+        <v>-220.3457240000328</v>
       </c>
       <c r="D89">
-        <v>129.4927493424343</v>
+        <v>128.4182759999672</v>
       </c>
       <c r="E89">
-        <v>270.236</v>
+        <v>274.4639999999999</v>
       </c>
       <c r="F89">
-        <v>367.836</v>
+        <v>372.064</v>
       </c>
       <c r="G89">
         <v>23.3</v>
@@ -8585,37 +8585,37 @@
         <v>21.8</v>
       </c>
       <c r="M89">
-        <v>86.73572879999999</v>
+        <v>87.73269119999999</v>
       </c>
       <c r="N89">
-        <v>-64.93572879999999</v>
+        <v>-65.93269119999999</v>
       </c>
       <c r="O89">
-        <v>-10.389716608</v>
+        <v>-10.549230592</v>
       </c>
       <c r="P89">
-        <v>-54.54601219199999</v>
+        <v>-55.38346060799999</v>
       </c>
       <c r="Q89">
-        <v>-32.24601219199999</v>
+        <v>-33.083460608</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5012189302347454</v>
+        <v>0.5391705077543076</v>
       </c>
       <c r="T89">
-        <v>6.269012996635876</v>
+        <v>6.791430746355533</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.04021410839866029</v>
+        <v>0.03975712989413005</v>
       </c>
       <c r="W89">
-        <v>0.2263175132395959</v>
+        <v>0.2264252687709641</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2513381774916267</v>
+        <v>0.2484820618383128</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2639546974489654</v>
+        <v>0.2658546974489654</v>
       </c>
       <c r="C90">
-        <v>-220.3457240000328</v>
+        <v>-225.6305130732027</v>
       </c>
       <c r="D90">
-        <v>128.4182759999672</v>
+        <v>127.3614869267972</v>
       </c>
       <c r="E90">
-        <v>274.4639999999999</v>
+        <v>278.692</v>
       </c>
       <c r="F90">
-        <v>372.064</v>
+        <v>376.292</v>
       </c>
       <c r="G90">
         <v>23.3</v>
@@ -8667,37 +8667,37 @@
         <v>21.8</v>
       </c>
       <c r="M90">
-        <v>87.73269119999999</v>
+        <v>88.72965359999999</v>
       </c>
       <c r="N90">
-        <v>-65.93269119999999</v>
+        <v>-66.92965359999999</v>
       </c>
       <c r="O90">
-        <v>-10.549230592</v>
+        <v>-10.708744576</v>
       </c>
       <c r="P90">
-        <v>-55.38346060799999</v>
+        <v>-56.22090902399999</v>
       </c>
       <c r="Q90">
-        <v>-33.083460608</v>
+        <v>-33.920909024</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5391705077543076</v>
+        <v>0.5840223720956083</v>
       </c>
       <c r="T90">
-        <v>6.791430746355533</v>
+        <v>7.408833541478763</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.03975712989413005</v>
+        <v>0.0393104205694769</v>
       </c>
       <c r="W90">
-        <v>0.2264252687709641</v>
+        <v>0.2265306028297174</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2484820618383128</v>
+        <v>0.2456901285592306</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2658546974489654</v>
+        <v>0.2677546974489654</v>
       </c>
       <c r="C91">
-        <v>-225.6305130732027</v>
+        <v>-230.8980508996629</v>
       </c>
       <c r="D91">
-        <v>127.3614869267972</v>
+        <v>126.3219491003371</v>
       </c>
       <c r="E91">
-        <v>278.692</v>
+        <v>282.92</v>
       </c>
       <c r="F91">
-        <v>376.292</v>
+        <v>380.52</v>
       </c>
       <c r="G91">
         <v>23.3</v>
@@ -8749,37 +8749,37 @@
         <v>21.8</v>
       </c>
       <c r="M91">
-        <v>88.72965359999999</v>
+        <v>89.72661599999999</v>
       </c>
       <c r="N91">
-        <v>-66.92965359999999</v>
+        <v>-67.926616</v>
       </c>
       <c r="O91">
-        <v>-10.708744576</v>
+        <v>-10.86825856</v>
       </c>
       <c r="P91">
-        <v>-56.22090902399999</v>
+        <v>-57.05835743999999</v>
       </c>
       <c r="Q91">
-        <v>-33.920909024</v>
+        <v>-34.75835744</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5840223720956083</v>
+        <v>0.6378446093051692</v>
       </c>
       <c r="T91">
-        <v>7.408833541478763</v>
+        <v>8.149716895626641</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.0393104205694769</v>
+        <v>0.03887363811870494</v>
       </c>
       <c r="W91">
-        <v>0.2265306028297174</v>
+        <v>0.2266335961316094</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2456901285592306</v>
+        <v>0.2429602382419058</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2677546974489654</v>
+        <v>0.2696546974489654</v>
       </c>
       <c r="C92">
-        <v>-230.8980508996629</v>
+        <v>-236.148756478955</v>
       </c>
       <c r="D92">
-        <v>126.3219491003371</v>
+        <v>125.299243521045</v>
       </c>
       <c r="E92">
-        <v>282.92</v>
+        <v>287.148</v>
       </c>
       <c r="F92">
-        <v>380.52</v>
+        <v>384.748</v>
       </c>
       <c r="G92">
         <v>23.3</v>
@@ -8831,37 +8831,37 @@
         <v>21.8</v>
       </c>
       <c r="M92">
-        <v>89.72661599999999</v>
+        <v>90.72357840000001</v>
       </c>
       <c r="N92">
-        <v>-67.926616</v>
+        <v>-68.92357840000001</v>
       </c>
       <c r="O92">
-        <v>-10.86825856</v>
+        <v>-11.027772544</v>
       </c>
       <c r="P92">
-        <v>-57.05835743999999</v>
+        <v>-57.89580585600001</v>
       </c>
       <c r="Q92">
-        <v>-34.75835744</v>
+        <v>-35.59580585600001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6378446093051692</v>
+        <v>0.7036273436724103</v>
       </c>
       <c r="T92">
-        <v>8.149716895626641</v>
+        <v>9.055240995140712</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.03887363811870494</v>
+        <v>0.03844645528223565</v>
       </c>
       <c r="W92">
-        <v>0.2266335961316094</v>
+        <v>0.2267343258444488</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2429602382419058</v>
+        <v>0.2402903455139728</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2696546974489654</v>
+        <v>0.2715546974489654</v>
       </c>
       <c r="C93">
-        <v>-236.148756478955</v>
+        <v>-241.3830353506707</v>
       </c>
       <c r="D93">
-        <v>125.299243521045</v>
+        <v>124.2929646493293</v>
       </c>
       <c r="E93">
-        <v>287.148</v>
+        <v>291.376</v>
       </c>
       <c r="F93">
-        <v>384.748</v>
+        <v>388.976</v>
       </c>
       <c r="G93">
         <v>23.3</v>
@@ -8913,37 +8913,37 @@
         <v>21.8</v>
       </c>
       <c r="M93">
-        <v>90.72357840000001</v>
+        <v>91.72054080000001</v>
       </c>
       <c r="N93">
-        <v>-68.92357840000001</v>
+        <v>-69.92054080000001</v>
       </c>
       <c r="O93">
-        <v>-11.027772544</v>
+        <v>-11.187286528</v>
       </c>
       <c r="P93">
-        <v>-57.89580585600001</v>
+        <v>-58.73325427200001</v>
       </c>
       <c r="Q93">
-        <v>-35.59580585600001</v>
+        <v>-36.43325427200001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7036273436724103</v>
+        <v>0.7858557616314618</v>
       </c>
       <c r="T93">
-        <v>9.055240995140712</v>
+        <v>10.1871461195333</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.03844645528223565</v>
+        <v>0.03802855902916787</v>
       </c>
       <c r="W93">
-        <v>0.2267343258444488</v>
+        <v>0.2268328657809222</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2402903455139728</v>
+        <v>0.2376784939322991</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2715546974489654</v>
+        <v>0.2734546974489653</v>
       </c>
       <c r="C94">
-        <v>-241.3830353506707</v>
+        <v>-246.6012801306305</v>
       </c>
       <c r="D94">
-        <v>124.2929646493293</v>
+        <v>123.3027198693695</v>
       </c>
       <c r="E94">
-        <v>291.376</v>
+        <v>295.6039999999999</v>
       </c>
       <c r="F94">
-        <v>388.976</v>
+        <v>393.204</v>
       </c>
       <c r="G94">
         <v>23.3</v>
@@ -8995,37 +8995,37 @@
         <v>21.8</v>
       </c>
       <c r="M94">
-        <v>91.72054080000001</v>
+        <v>92.7175032</v>
       </c>
       <c r="N94">
-        <v>-69.92054080000001</v>
+        <v>-70.9175032</v>
       </c>
       <c r="O94">
-        <v>-11.187286528</v>
+        <v>-11.346800512</v>
       </c>
       <c r="P94">
-        <v>-58.73325427200001</v>
+        <v>-59.570702688</v>
       </c>
       <c r="Q94">
-        <v>-36.43325427200001</v>
+        <v>-37.270702688</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7858557616314618</v>
+        <v>0.8915780132930992</v>
       </c>
       <c r="T94">
-        <v>10.1871461195333</v>
+        <v>11.64245270803806</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.03802855902916787</v>
+        <v>0.0376196497922951</v>
       </c>
       <c r="W94">
-        <v>0.2268328657809222</v>
+        <v>0.2269292865789768</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2376784939322991</v>
+        <v>0.2351228112018443</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2734546974489653</v>
+        <v>0.2753546974489654</v>
       </c>
       <c r="C95">
-        <v>-246.6012801306305</v>
+        <v>-251.8038710216342</v>
       </c>
       <c r="D95">
-        <v>123.3027198693695</v>
+        <v>122.3281289783658</v>
       </c>
       <c r="E95">
-        <v>295.6039999999999</v>
+        <v>299.832</v>
       </c>
       <c r="F95">
-        <v>393.204</v>
+        <v>397.432</v>
       </c>
       <c r="G95">
         <v>23.3</v>
@@ -9077,37 +9077,37 @@
         <v>21.8</v>
       </c>
       <c r="M95">
-        <v>92.7175032</v>
+        <v>93.7144656</v>
       </c>
       <c r="N95">
-        <v>-70.9175032</v>
+        <v>-71.9144656</v>
       </c>
       <c r="O95">
-        <v>-11.346800512</v>
+        <v>-11.506314496</v>
       </c>
       <c r="P95">
-        <v>-59.570702688</v>
+        <v>-60.408151104</v>
       </c>
       <c r="Q95">
-        <v>-37.270702688</v>
+        <v>-38.108151104</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8915780132930992</v>
+        <v>1.032541015508616</v>
       </c>
       <c r="T95">
-        <v>11.64245270803806</v>
+        <v>13.58286149271108</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.0376196497922951</v>
+        <v>0.03721944075195154</v>
       </c>
       <c r="W95">
-        <v>0.2269292865789768</v>
+        <v>0.2270236558706898</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2351228112018443</v>
+        <v>0.232621504699697</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2753546974489654</v>
+        <v>0.2772546974489654</v>
       </c>
       <c r="C96">
-        <v>-251.8038710216342</v>
+        <v>-256.9911763001795</v>
       </c>
       <c r="D96">
-        <v>122.3281289783658</v>
+        <v>121.3688236998204</v>
       </c>
       <c r="E96">
-        <v>299.832</v>
+        <v>304.0599999999999</v>
       </c>
       <c r="F96">
-        <v>397.432</v>
+        <v>401.66</v>
       </c>
       <c r="G96">
         <v>23.3</v>
@@ -9159,37 +9159,37 @@
         <v>21.8</v>
       </c>
       <c r="M96">
-        <v>93.7144656</v>
+        <v>94.711428</v>
       </c>
       <c r="N96">
-        <v>-71.9144656</v>
+        <v>-72.911428</v>
       </c>
       <c r="O96">
-        <v>-11.506314496</v>
+        <v>-11.66582848</v>
       </c>
       <c r="P96">
-        <v>-60.408151104</v>
+        <v>-61.24559952</v>
       </c>
       <c r="Q96">
-        <v>-38.108151104</v>
+        <v>-38.94559952</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.032541015508616</v>
+        <v>1.22988921861034</v>
       </c>
       <c r="T96">
-        <v>13.58286149271108</v>
+        <v>16.2994337912533</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.03721944075195154</v>
+        <v>0.03682765716508889</v>
       </c>
       <c r="W96">
-        <v>0.2270236558706898</v>
+        <v>0.2271160384404721</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.232621504699697</v>
+        <v>0.2301728572818055</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2772546974489654</v>
+        <v>0.2791546974489654</v>
       </c>
       <c r="C97">
-        <v>-256.9911763001795</v>
+        <v>-262.1635527804577</v>
       </c>
       <c r="D97">
-        <v>121.3688236998204</v>
+        <v>120.4244472195423</v>
       </c>
       <c r="E97">
-        <v>304.0599999999999</v>
+        <v>308.288</v>
       </c>
       <c r="F97">
-        <v>401.66</v>
+        <v>405.888</v>
       </c>
       <c r="G97">
         <v>23.3</v>
@@ -9241,37 +9241,37 @@
         <v>21.8</v>
       </c>
       <c r="M97">
-        <v>94.711428</v>
+        <v>95.7083904</v>
       </c>
       <c r="N97">
-        <v>-72.911428</v>
+        <v>-73.9083904</v>
       </c>
       <c r="O97">
-        <v>-11.66582848</v>
+        <v>-11.825342464</v>
       </c>
       <c r="P97">
-        <v>-61.24559952</v>
+        <v>-62.083047936</v>
       </c>
       <c r="Q97">
-        <v>-38.94559952</v>
+        <v>-39.783047936</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.22988921861034</v>
+        <v>1.525911523262926</v>
       </c>
       <c r="T97">
-        <v>16.2994337912533</v>
+        <v>20.37429223906664</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.03682765716508889</v>
+        <v>0.03644403573628588</v>
       </c>
       <c r="W97">
-        <v>0.2271160384404721</v>
+        <v>0.2272064963733838</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2301728572818055</v>
+        <v>0.2277752233517867</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2791546974489654</v>
+        <v>0.2810546974489654</v>
       </c>
       <c r="C98">
-        <v>-262.1635527804576</v>
+        <v>-267.3213462568542</v>
       </c>
       <c r="D98">
-        <v>120.4244472195423</v>
+        <v>119.4946537431458</v>
       </c>
       <c r="E98">
-        <v>308.2879999999999</v>
+        <v>312.516</v>
       </c>
       <c r="F98">
-        <v>405.8879999999999</v>
+        <v>410.1159999999999</v>
       </c>
       <c r="G98">
         <v>23.3</v>
@@ -9323,37 +9323,37 @@
         <v>21.8</v>
       </c>
       <c r="M98">
-        <v>95.70839039999998</v>
+        <v>96.70535279999999</v>
       </c>
       <c r="N98">
-        <v>-73.90839039999999</v>
+        <v>-74.90535279999999</v>
       </c>
       <c r="O98">
-        <v>-11.825342464</v>
+        <v>-11.984856448</v>
       </c>
       <c r="P98">
-        <v>-62.08304793599999</v>
+        <v>-62.92049635199999</v>
       </c>
       <c r="Q98">
-        <v>-39.78304793599999</v>
+        <v>-40.62049635199999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.525911523262922</v>
+        <v>2.019282031017229</v>
       </c>
       <c r="T98">
-        <v>20.37429223906658</v>
+        <v>27.16572298542211</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.03644403573628589</v>
+        <v>0.03606832402766438</v>
       </c>
       <c r="W98">
-        <v>0.2272064963733838</v>
+        <v>0.2272950891942768</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2277752233517867</v>
+        <v>0.2254270251729024</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2810546974489654</v>
+        <v>0.2829546974489653</v>
       </c>
       <c r="C99">
-        <v>-267.3213462568542</v>
+        <v>-272.464891926107</v>
       </c>
       <c r="D99">
-        <v>119.4946537431458</v>
+        <v>118.5791080738929</v>
       </c>
       <c r="E99">
-        <v>312.516</v>
+        <v>316.7439999999999</v>
       </c>
       <c r="F99">
-        <v>410.1159999999999</v>
+        <v>414.3439999999999</v>
       </c>
       <c r="G99">
         <v>23.3</v>
@@ -9405,37 +9405,37 @@
         <v>21.8</v>
       </c>
       <c r="M99">
-        <v>96.70535279999999</v>
+        <v>97.70231519999999</v>
       </c>
       <c r="N99">
-        <v>-74.90535279999999</v>
+        <v>-75.90231519999999</v>
       </c>
       <c r="O99">
-        <v>-11.984856448</v>
+        <v>-12.144370432</v>
       </c>
       <c r="P99">
-        <v>-62.92049635199999</v>
+        <v>-63.75794476799999</v>
       </c>
       <c r="Q99">
-        <v>-40.62049635199999</v>
+        <v>-41.45794476799999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.019282031017229</v>
+        <v>3.006023046525843</v>
       </c>
       <c r="T99">
-        <v>27.16572298542211</v>
+        <v>40.74858447813316</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.03606832402766438</v>
+        <v>0.03570027990493311</v>
       </c>
       <c r="W99">
-        <v>0.2272950891942768</v>
+        <v>0.2273818739984168</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2254270251729024</v>
+        <v>0.2231267494058319</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2829546974489653</v>
+        <v>0.2848546974489653</v>
       </c>
       <c r="C100">
-        <v>-272.464891926107</v>
+        <v>-277.5945147902059</v>
       </c>
       <c r="D100">
-        <v>118.5791080738929</v>
+        <v>117.6774852097941</v>
       </c>
       <c r="E100">
-        <v>316.7439999999999</v>
+        <v>320.972</v>
       </c>
       <c r="F100">
-        <v>414.3439999999999</v>
+        <v>418.5719999999999</v>
       </c>
       <c r="G100">
         <v>23.3</v>
@@ -9487,37 +9487,37 @@
         <v>21.8</v>
       </c>
       <c r="M100">
-        <v>97.70231519999999</v>
+        <v>98.69927759999999</v>
       </c>
       <c r="N100">
-        <v>-75.90231519999999</v>
+        <v>-76.89927759999999</v>
       </c>
       <c r="O100">
-        <v>-12.144370432</v>
+        <v>-12.303884416</v>
       </c>
       <c r="P100">
-        <v>-63.75794476799999</v>
+        <v>-64.59539318399999</v>
       </c>
       <c r="Q100">
-        <v>-41.45794476799999</v>
+        <v>-42.29539318399999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.006023046525843</v>
+        <v>5.966246093051686</v>
       </c>
       <c r="T100">
-        <v>40.74858447813316</v>
+        <v>81.49716895626632</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.03570027990493311</v>
+        <v>0.03533967101700449</v>
       </c>
       <c r="W100">
-        <v>0.2273818739984168</v>
+        <v>0.2274669055741903</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2231267494058319</v>
+        <v>0.220872943856278</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2848546974489653</v>
-      </c>
-      <c r="C101">
-        <v>-277.5945147902059</v>
-      </c>
-      <c r="D101">
-        <v>117.6774852097941</v>
-      </c>
-      <c r="E101">
-        <v>320.972</v>
-      </c>
-      <c r="F101">
-        <v>418.5719999999999</v>
-      </c>
-      <c r="G101">
-        <v>23.3</v>
-      </c>
-      <c r="H101">
-        <v>325.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>44.1</v>
-      </c>
-      <c r="K101">
-        <v>22.3</v>
-      </c>
-      <c r="L101">
-        <v>21.8</v>
-      </c>
-      <c r="M101">
-        <v>98.69927759999999</v>
-      </c>
-      <c r="N101">
-        <v>-76.89927759999999</v>
-      </c>
-      <c r="O101">
-        <v>-12.303884416</v>
-      </c>
-      <c r="P101">
-        <v>-64.59539318399999</v>
-      </c>
-      <c r="Q101">
-        <v>-42.29539318399999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.966246093051686</v>
-      </c>
-      <c r="T101">
-        <v>81.49716895626632</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.03533967101700449</v>
-      </c>
-      <c r="W101">
-        <v>0.2274669055741903</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.220872943856278</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
